--- a/Resources/WeaponsStats.xlsx
+++ b/Resources/WeaponsStats.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="28695" windowHeight="12540" tabRatio="807" activeTab="3"/>
+    <workbookView xWindow="120" yWindow="105" windowWidth="28695" windowHeight="12540" tabRatio="807" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Handgun" sheetId="8" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1572" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1561" uniqueCount="520">
   <si>
     <t>Weapon Stats - Sleepy's Weapons</t>
   </si>
@@ -1314,16 +1314,10 @@
     <t>105mm Cannon</t>
   </si>
   <si>
-    <t>127mm Cannon</t>
-  </si>
-  <si>
     <t>155mm Cannon</t>
   </si>
   <si>
     <t>203mm Cannon</t>
-  </si>
-  <si>
-    <t>305mm Cannon</t>
   </si>
   <si>
     <t>40mm Turret</t>
@@ -2009,13 +2003,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="1" builtinId="10"/>
   </cellStyles>
-  <dxfs count="384">
-    <dxf>
-      <font>
-        <strike/>
-        <color theme="0"/>
-      </font>
-    </dxf>
+  <dxfs count="383">
     <dxf>
       <fill>
         <patternFill>
@@ -4740,17 +4728,17 @@
   <tableColumns count="25">
     <tableColumn id="1" name="Weapon Name"/>
     <tableColumn id="12" name="Vol."/>
-    <tableColumn id="22" name="Balance" dataDxfId="366">
+    <tableColumn id="22" name="Balance" dataDxfId="365">
       <calculatedColumnFormula>SUM(((Table1689[[#This Row],[Avg DPS]]*(Table1689[[#This Row],[Range]]))+(Table1689[[#This Row],[Avg DPS]]*(Table1689[[#This Row],[Arm Pen (%)]]/4)))/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Avg DPS" dataDxfId="365">
+    <tableColumn id="20" name="Avg DPS" dataDxfId="364">
       <calculatedColumnFormula>SUM(Table1689[[#This Row],[DPS]]*Table1689[[#This Row],[Avg Accuracy]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="364">
+    <tableColumn id="15" name="DPS" dataDxfId="363">
       <calculatedColumnFormula>SUM((Table1689[[#This Row],[Damage]]*Table1689[[#This Row],[Burst]])/(Table1689[[#This Row],[Ranged Cooldown]]+Table1689[[#This Row],[Warm-up]]+(Table1689[[#This Row],[Burst Time]]*(Table1689[[#This Row],[Burst]]-1))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" name="Range"/>
-    <tableColumn id="17" name="Avg Accuracy" dataDxfId="363">
+    <tableColumn id="17" name="Avg Accuracy" dataDxfId="362">
       <calculatedColumnFormula>SUM((Table1689[[#This Row],[Accuracy (Close)]]+Table1689[[#This Row],[Accuracy (Short)]]+Table1689[[#This Row],[Accuracy (Medium)]]+Table1689[[#This Row],[Accuracy (Long)]])/4)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" name="Damage"/>
@@ -4760,7 +4748,7 @@
     <tableColumn id="4" name="Ranged Cooldown"/>
     <tableColumn id="5" name="Warm-up"/>
     <tableColumn id="6" name="RPM"/>
-    <tableColumn id="7" name="Burst Time" dataDxfId="362">
+    <tableColumn id="7" name="Burst Time" dataDxfId="361">
       <calculatedColumnFormula>60/N4</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" name="Accuracy (Close)"/>
@@ -4779,7 +4767,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table16810111213" displayName="Table16810111213" ref="A3:Y19" totalsRowShown="0" dataDxfId="132">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Table16810111213" displayName="Table16810111213" ref="A3:Y19" totalsRowShown="0" dataDxfId="131">
   <autoFilter ref="A3:Y19">
     <filterColumn colId="1"/>
     <filterColumn colId="2"/>
@@ -4800,50 +4788,50 @@
     <sortCondition ref="B3:B19"/>
   </sortState>
   <tableColumns count="25">
-    <tableColumn id="1" name="Weapon Name" dataDxfId="131"/>
-    <tableColumn id="12" name="Vol." dataDxfId="130"/>
-    <tableColumn id="22" name="Balance" dataDxfId="129">
+    <tableColumn id="1" name="Weapon Name" dataDxfId="130"/>
+    <tableColumn id="12" name="Vol." dataDxfId="129"/>
+    <tableColumn id="22" name="Balance" dataDxfId="128">
       <calculatedColumnFormula>SUM(((Table16810111213[[#This Row],[Avg DPS]]*(Table16810111213[[#This Row],[Range]]))+(Table16810111213[[#This Row],[Avg DPS]]*(Table16810111213[[#This Row],[Arm Pen (%)]]/4)))/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Avg DPS" dataDxfId="128">
+    <tableColumn id="20" name="Avg DPS" dataDxfId="127">
       <calculatedColumnFormula>SUM(Table16810111213[[#This Row],[DPS]]*Table16810111213[[#This Row],[Avg Accuracy]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="127">
+    <tableColumn id="15" name="DPS" dataDxfId="126">
       <calculatedColumnFormula>SUM((Table16810111213[[#This Row],[Damage]]*Table16810111213[[#This Row],[Burst]])/(Table16810111213[[#This Row],[Ranged Cooldown]]+Table16810111213[[#This Row],[Warm-up]]+(Table16810111213[[#This Row],[Burst Time]]*(Table16810111213[[#This Row],[Burst]]-1))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" name="Range" dataDxfId="126"/>
-    <tableColumn id="17" name="Avg Accuracy" dataDxfId="125">
+    <tableColumn id="16" name="Range" dataDxfId="125"/>
+    <tableColumn id="17" name="Avg Accuracy" dataDxfId="124">
       <calculatedColumnFormula>SUM((Table16810111213[[#This Row],[Accuracy (Close)]]+Table16810111213[[#This Row],[Accuracy (Short)]]+Table16810111213[[#This Row],[Accuracy (Medium)]]+Table16810111213[[#This Row],[Accuracy (Long)]])/4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="Damage" dataDxfId="124"/>
-    <tableColumn id="18" name="Stopping Pwr" dataDxfId="123"/>
-    <tableColumn id="19" name="Arm Pen (%)" dataDxfId="122"/>
-    <tableColumn id="3" name="Burst" dataDxfId="121"/>
-    <tableColumn id="4" name="Ranged Cooldown" dataDxfId="120"/>
-    <tableColumn id="5" name="Warm-up" dataDxfId="119"/>
-    <tableColumn id="6" name="RPM" dataDxfId="118"/>
-    <tableColumn id="7" name="Burst Time" dataDxfId="117">
+    <tableColumn id="2" name="Damage" dataDxfId="123"/>
+    <tableColumn id="18" name="Stopping Pwr" dataDxfId="122"/>
+    <tableColumn id="19" name="Arm Pen (%)" dataDxfId="121"/>
+    <tableColumn id="3" name="Burst" dataDxfId="120"/>
+    <tableColumn id="4" name="Ranged Cooldown" dataDxfId="119"/>
+    <tableColumn id="5" name="Warm-up" dataDxfId="118"/>
+    <tableColumn id="6" name="RPM" dataDxfId="117"/>
+    <tableColumn id="7" name="Burst Time" dataDxfId="116">
       <calculatedColumnFormula>60/N4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="Accuracy (Close)" dataDxfId="116"/>
-    <tableColumn id="9" name="Accuracy (Short)" dataDxfId="115"/>
-    <tableColumn id="10" name="Accuracy (Medium)" dataDxfId="114"/>
-    <tableColumn id="11" name="Accuracy (Long)" dataDxfId="113"/>
-    <tableColumn id="13" name="Bullet Speed" dataDxfId="112"/>
-    <tableColumn id="14" name="Weight" dataDxfId="111"/>
-    <tableColumn id="21" name="Craftable" dataDxfId="110"/>
-    <tableColumn id="23" name="Value" dataDxfId="109">
+    <tableColumn id="8" name="Accuracy (Close)" dataDxfId="115"/>
+    <tableColumn id="9" name="Accuracy (Short)" dataDxfId="114"/>
+    <tableColumn id="10" name="Accuracy (Medium)" dataDxfId="113"/>
+    <tableColumn id="11" name="Accuracy (Long)" dataDxfId="112"/>
+    <tableColumn id="13" name="Bullet Speed" dataDxfId="111"/>
+    <tableColumn id="14" name="Weight" dataDxfId="110"/>
+    <tableColumn id="21" name="Craftable" dataDxfId="109"/>
+    <tableColumn id="23" name="Value" dataDxfId="108">
       <calculatedColumnFormula>Table16810111213[[#This Row],[Balance]]*$W$1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" name="SoundShoot" dataDxfId="108"/>
-    <tableColumn id="25" name="SoundInteract" dataDxfId="107"/>
+    <tableColumn id="24" name="SoundShoot" dataDxfId="107"/>
+    <tableColumn id="25" name="SoundInteract" dataDxfId="106"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Table1681011121317" displayName="Table1681011121317" ref="A3:Y19" totalsRowShown="0" dataDxfId="87">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Table1681011121317" displayName="Table1681011121317" ref="A3:Y19" totalsRowShown="0" dataDxfId="86">
   <autoFilter ref="A3:Y19">
     <filterColumn colId="1"/>
     <filterColumn colId="2"/>
@@ -4864,43 +4852,43 @@
     <sortCondition ref="B3:B19"/>
   </sortState>
   <tableColumns count="25">
-    <tableColumn id="1" name="Weapon Name" dataDxfId="86"/>
-    <tableColumn id="12" name="Vol." dataDxfId="85"/>
-    <tableColumn id="22" name="Balance" dataDxfId="84">
+    <tableColumn id="1" name="Weapon Name" dataDxfId="85"/>
+    <tableColumn id="12" name="Vol." dataDxfId="84"/>
+    <tableColumn id="22" name="Balance" dataDxfId="83">
       <calculatedColumnFormula>SUM(((Table1681011121317[[#This Row],[Avg DPS]]*(Table1681011121317[[#This Row],[Range]]))+(Table1681011121317[[#This Row],[Avg DPS]]*(Table1681011121317[[#This Row],[Arm Pen (%)]]/4)))/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Avg DPS" dataDxfId="83">
+    <tableColumn id="20" name="Avg DPS" dataDxfId="82">
       <calculatedColumnFormula>SUM(Table1681011121317[[#This Row],[DPS]]*Table1681011121317[[#This Row],[Avg Accuracy]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="82">
+    <tableColumn id="15" name="DPS" dataDxfId="81">
       <calculatedColumnFormula>SUM((Table1681011121317[[#This Row],[Damage]]*Table1681011121317[[#This Row],[Burst]])/(Table1681011121317[[#This Row],[Ranged Cooldown]]+Table1681011121317[[#This Row],[Warm-up]]+(Table1681011121317[[#This Row],[Burst Time]]*(Table1681011121317[[#This Row],[Burst]]-1))))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" name="Range" dataDxfId="81"/>
-    <tableColumn id="17" name="Avg Accuracy" dataDxfId="80">
+    <tableColumn id="16" name="Range" dataDxfId="80"/>
+    <tableColumn id="17" name="Avg Accuracy" dataDxfId="79">
       <calculatedColumnFormula>SUM((Table1681011121317[[#This Row],[Accuracy (Close)]]+Table1681011121317[[#This Row],[Accuracy (Short)]]+Table1681011121317[[#This Row],[Accuracy (Medium)]]+Table1681011121317[[#This Row],[Accuracy (Long)]])/4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="Damage" dataDxfId="79"/>
-    <tableColumn id="18" name="Stopping Pwr" dataDxfId="78"/>
-    <tableColumn id="19" name="Arm Pen (%)" dataDxfId="77"/>
-    <tableColumn id="3" name="Burst" dataDxfId="76"/>
-    <tableColumn id="4" name="Ranged Cooldown" dataDxfId="75"/>
-    <tableColumn id="5" name="Warm-up" dataDxfId="74"/>
-    <tableColumn id="6" name="RPM" dataDxfId="73"/>
-    <tableColumn id="7" name="Burst Time" dataDxfId="72">
+    <tableColumn id="2" name="Damage" dataDxfId="78"/>
+    <tableColumn id="18" name="Stopping Pwr" dataDxfId="77"/>
+    <tableColumn id="19" name="Arm Pen (%)" dataDxfId="76"/>
+    <tableColumn id="3" name="Burst" dataDxfId="75"/>
+    <tableColumn id="4" name="Ranged Cooldown" dataDxfId="74"/>
+    <tableColumn id="5" name="Warm-up" dataDxfId="73"/>
+    <tableColumn id="6" name="RPM" dataDxfId="72"/>
+    <tableColumn id="7" name="Burst Time" dataDxfId="71">
       <calculatedColumnFormula>60/N4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" name="Accuracy (Close)" dataDxfId="71"/>
-    <tableColumn id="9" name="Accuracy (Short)" dataDxfId="70"/>
-    <tableColumn id="10" name="Accuracy (Medium)" dataDxfId="69"/>
-    <tableColumn id="11" name="Accuracy (Long)" dataDxfId="68"/>
-    <tableColumn id="13" name="Bullet Speed" dataDxfId="67"/>
-    <tableColumn id="14" name="Weight" dataDxfId="66"/>
-    <tableColumn id="21" name="Craftable" dataDxfId="65"/>
-    <tableColumn id="23" name="Value" dataDxfId="64">
+    <tableColumn id="8" name="Accuracy (Close)" dataDxfId="70"/>
+    <tableColumn id="9" name="Accuracy (Short)" dataDxfId="69"/>
+    <tableColumn id="10" name="Accuracy (Medium)" dataDxfId="68"/>
+    <tableColumn id="11" name="Accuracy (Long)" dataDxfId="67"/>
+    <tableColumn id="13" name="Bullet Speed" dataDxfId="66"/>
+    <tableColumn id="14" name="Weight" dataDxfId="65"/>
+    <tableColumn id="21" name="Craftable" dataDxfId="64"/>
+    <tableColumn id="23" name="Value" dataDxfId="63">
       <calculatedColumnFormula>Table1681011121317[[#This Row],[Balance]]*$W$1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" name="SoundShoot" dataDxfId="63"/>
-    <tableColumn id="25" name="SoundInteract" dataDxfId="62"/>
+    <tableColumn id="24" name="SoundShoot" dataDxfId="62"/>
+    <tableColumn id="25" name="SoundInteract" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4928,13 +4916,13 @@
   <tableColumns count="25">
     <tableColumn id="1" name="Weapon Name"/>
     <tableColumn id="12" name="Vol."/>
-    <tableColumn id="22" name="Balance" dataDxfId="60">
+    <tableColumn id="22" name="Balance" dataDxfId="59">
       <calculatedColumnFormula>SUM(((Table168101112133[[#This Row],[DPS]]*Table168101112133[[#This Row],[Avg Cooldown]])+((Table168101112133[[#This Row],[DPS]]*(Table168101112133[[#This Row],[HPM]])))+P4)/100)+(Table168101112133[[#This Row],[ArmPen+]]/5)+(Table168101112133[[#This Row],[ExtraDamFactor]]/20)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="59">
+    <tableColumn id="15" name="DPS" dataDxfId="58">
       <calculatedColumnFormula>SUM(Table168101112133[[#This Row],[Avg DAM]]*Table168101112133[[#This Row],[HPS]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Avg DAM" dataDxfId="58">
+    <tableColumn id="3" name="Avg DAM" dataDxfId="57">
       <calculatedColumnFormula>Formulas!U5</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" name="Damage 1"/>
@@ -4946,33 +4934,33 @@
     <tableColumn id="25" name="Damage 4"/>
     <tableColumn id="30" name="Cooldown 4"/>
     <tableColumn id="34" name="Extra Dam"/>
-    <tableColumn id="32" name="Extra Dam C%" dataDxfId="57"/>
-    <tableColumn id="33" name="ExtraDamFactor" dataDxfId="56">
+    <tableColumn id="32" name="Extra Dam C%" dataDxfId="56"/>
+    <tableColumn id="33" name="ExtraDamFactor" dataDxfId="55">
       <calculatedColumnFormula>IF(Table168101112133[[#This Row],[Extra Dam C%]]="N/A",0,SUM((Table168101112133[[#This Row],[Extra Dam C%]]*Table168101112133[[#This Row],[Extra Dam]])))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="31" name="ArmPen+"/>
-    <tableColumn id="4" name="Avg Cooldown" dataDxfId="55">
+    <tableColumn id="4" name="Avg Cooldown" dataDxfId="54">
       <calculatedColumnFormula>Formulas!AP5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" name="HPM" dataDxfId="54">
+    <tableColumn id="6" name="HPM" dataDxfId="53">
       <calculatedColumnFormula>SUM(60/Table168101112133[[#This Row],[Avg Cooldown]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="HPS" dataDxfId="53">
+    <tableColumn id="7" name="HPS" dataDxfId="52">
       <calculatedColumnFormula>SUM(Table168101112133[[#This Row],[HPM]]/60)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" name="Weight" dataDxfId="52"/>
+    <tableColumn id="14" name="Weight" dataDxfId="51"/>
     <tableColumn id="21" name="Craftable"/>
-    <tableColumn id="5" name="Value" dataDxfId="51"/>
-    <tableColumn id="8" name="SoundShoot" dataDxfId="50"/>
-    <tableColumn id="9" name="SoundInteract" dataDxfId="49"/>
+    <tableColumn id="5" name="Value" dataDxfId="50"/>
+    <tableColumn id="8" name="SoundShoot" dataDxfId="49"/>
+    <tableColumn id="9" name="SoundInteract" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table16810111245" displayName="Table16810111245" ref="A3:AJ50" totalsRowShown="0">
-  <autoFilter ref="A3:AJ50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table16810111245" displayName="Table16810111245" ref="A3:AJ48" totalsRowShown="0">
+  <autoFilter ref="A3:AJ48">
     <filterColumn colId="19"/>
     <filterColumn colId="22"/>
     <filterColumn colId="23"/>
@@ -4993,18 +4981,18 @@
   </sortState>
   <tableColumns count="36">
     <tableColumn id="1" name="Weapon Name"/>
-    <tableColumn id="12" name="Vol." dataDxfId="48"/>
-    <tableColumn id="22" name="Balance" dataDxfId="47">
+    <tableColumn id="12" name="Vol." dataDxfId="47"/>
+    <tableColumn id="22" name="Balance" dataDxfId="46">
       <calculatedColumnFormula>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Avg DPS" dataDxfId="46">
+    <tableColumn id="20" name="Avg DPS" dataDxfId="45">
       <calculatedColumnFormula>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="45">
+    <tableColumn id="15" name="DPS" dataDxfId="44">
       <calculatedColumnFormula>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" name="Range"/>
-    <tableColumn id="17" name="Avg Accuracy" dataDxfId="44">
+    <tableColumn id="17" name="Avg Accuracy" dataDxfId="43">
       <calculatedColumnFormula>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" name="Damage"/>
@@ -5014,7 +5002,7 @@
     <tableColumn id="4" name="Ranged Cooldown"/>
     <tableColumn id="5" name="Warm-up"/>
     <tableColumn id="6" name="RPM"/>
-    <tableColumn id="7" name="Burst Time" dataDxfId="43">
+    <tableColumn id="7" name="Burst Time" dataDxfId="42">
       <calculatedColumnFormula>60/N4</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" name="Accuracy (Close)"/>
@@ -5025,19 +5013,19 @@
     <tableColumn id="13" name="Bullet Speed"/>
     <tableColumn id="14" name="Weight"/>
     <tableColumn id="24" name="Rearm Cost"/>
-    <tableColumn id="33" name="Rearm Mat" dataDxfId="42"/>
+    <tableColumn id="33" name="Rearm Mat" dataDxfId="41"/>
     <tableColumn id="28" name="Ammo"/>
     <tableColumn id="31" name="Bursts"/>
     <tableColumn id="32" name="A.P.C."/>
     <tableColumn id="23" name="COG"/>
     <tableColumn id="25" name="Materials"/>
-    <tableColumn id="27" name="Minify?" dataDxfId="41"/>
-    <tableColumn id="30" name="Power" dataDxfId="40"/>
+    <tableColumn id="27" name="Minify?" dataDxfId="40"/>
+    <tableColumn id="30" name="Power" dataDxfId="39"/>
     <tableColumn id="26" name="Class"/>
     <tableColumn id="21" name="SoundShoot"/>
     <tableColumn id="34" name="SoundInteract"/>
-    <tableColumn id="35" name="ForcedMiss" dataDxfId="39"/>
-    <tableColumn id="37" name="Blast Range" dataDxfId="38"/>
+    <tableColumn id="35" name="ForcedMiss" dataDxfId="38"/>
+    <tableColumn id="37" name="Blast Range" dataDxfId="37"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5069,25 +5057,25 @@
   <tableColumns count="21">
     <tableColumn id="1" name="Weapon Name"/>
     <tableColumn id="12" name="Vol."/>
-    <tableColumn id="3" name="Range" dataDxfId="37"/>
-    <tableColumn id="4" name="Damage" dataDxfId="36"/>
-    <tableColumn id="5" name="AP" dataDxfId="35"/>
-    <tableColumn id="6" name="Stopping Power" dataDxfId="34"/>
-    <tableColumn id="15" name="ForcedMiss" dataDxfId="33"/>
-    <tableColumn id="11" name="DetDelay" dataDxfId="32"/>
-    <tableColumn id="10" name="Blast Range" dataDxfId="31"/>
-    <tableColumn id="8" name="Warm-Up" dataDxfId="30"/>
-    <tableColumn id="9" name="Cooldown" dataDxfId="29"/>
-    <tableColumn id="20" name="Burst" dataDxfId="28"/>
-    <tableColumn id="13" name="Bullet Speed" dataDxfId="27"/>
-    <tableColumn id="14" name="Weight" dataDxfId="26"/>
-    <tableColumn id="7" name="Single Use" dataDxfId="25"/>
-    <tableColumn id="21" name="Craftable" dataDxfId="24"/>
-    <tableColumn id="2" name="Accuracy" dataDxfId="23"/>
-    <tableColumn id="19" name="SoundAim" dataDxfId="22"/>
-    <tableColumn id="18" name="SoundShoot" dataDxfId="21"/>
-    <tableColumn id="16" name="SoundDamage" dataDxfId="20"/>
-    <tableColumn id="17" name="SoundInteract" dataDxfId="19"/>
+    <tableColumn id="3" name="Range" dataDxfId="36"/>
+    <tableColumn id="4" name="Damage" dataDxfId="35"/>
+    <tableColumn id="5" name="AP" dataDxfId="34"/>
+    <tableColumn id="6" name="Stopping Power" dataDxfId="33"/>
+    <tableColumn id="15" name="ForcedMiss" dataDxfId="32"/>
+    <tableColumn id="11" name="DetDelay" dataDxfId="31"/>
+    <tableColumn id="10" name="Blast Range" dataDxfId="30"/>
+    <tableColumn id="8" name="Warm-Up" dataDxfId="29"/>
+    <tableColumn id="9" name="Cooldown" dataDxfId="28"/>
+    <tableColumn id="20" name="Burst" dataDxfId="27"/>
+    <tableColumn id="13" name="Bullet Speed" dataDxfId="26"/>
+    <tableColumn id="14" name="Weight" dataDxfId="25"/>
+    <tableColumn id="7" name="Single Use" dataDxfId="24"/>
+    <tableColumn id="21" name="Craftable" dataDxfId="23"/>
+    <tableColumn id="2" name="Accuracy" dataDxfId="22"/>
+    <tableColumn id="19" name="SoundAim" dataDxfId="21"/>
+    <tableColumn id="18" name="SoundShoot" dataDxfId="20"/>
+    <tableColumn id="16" name="SoundDamage" dataDxfId="19"/>
+    <tableColumn id="17" name="SoundInteract" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5105,17 +5093,17 @@
   <tableColumns count="28">
     <tableColumn id="1" name="Weapon Name"/>
     <tableColumn id="12" name="Vol."/>
-    <tableColumn id="22" name="Balance" dataDxfId="17">
+    <tableColumn id="22" name="Balance" dataDxfId="16">
       <calculatedColumnFormula>SUM(((Table1681011124[[#This Row],[Avg DPS]]*(Table1681011124[[#This Row],[Range]]))+(Table1681011124[[#This Row],[Avg DPS]]*(Table1681011124[[#This Row],[Arm Pen (%)]]/4)))/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Avg DPS" dataDxfId="16">
+    <tableColumn id="20" name="Avg DPS" dataDxfId="15">
       <calculatedColumnFormula>SUM(Table1681011124[[#This Row],[DPS]]*Table1681011124[[#This Row],[Avg Accuracy]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="15">
+    <tableColumn id="15" name="DPS" dataDxfId="14">
       <calculatedColumnFormula>SUM((Table1681011124[[#This Row],[Damage]]*Table1681011124[[#This Row],[Burst]])/(Table1681011124[[#This Row],[Ranged Cooldown]]+Table1681011124[[#This Row],[Warm-up]]+(Table1681011124[[#This Row],[Burst Time]]*(Table1681011124[[#This Row],[Burst]]-1))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" name="Range"/>
-    <tableColumn id="17" name="Avg Accuracy" dataDxfId="14">
+    <tableColumn id="17" name="Avg Accuracy" dataDxfId="13">
       <calculatedColumnFormula>SUM((Table1681011124[[#This Row],[Accuracy (Close)]]+Table1681011124[[#This Row],[Accuracy (Short)]]+Table1681011124[[#This Row],[Accuracy (Medium)]]+Table1681011124[[#This Row],[Accuracy (Long)]])/4)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" name="Damage"/>
@@ -5125,7 +5113,7 @@
     <tableColumn id="4" name="Ranged Cooldown"/>
     <tableColumn id="5" name="Warm-up"/>
     <tableColumn id="6" name="RPM"/>
-    <tableColumn id="7" name="Burst Time" dataDxfId="13">
+    <tableColumn id="7" name="Burst Time" dataDxfId="12">
       <calculatedColumnFormula>60/N4</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" name="Accuracy (Close)"/>
@@ -5169,18 +5157,18 @@
   </sortState>
   <tableColumns count="25">
     <tableColumn id="1" name="Weapon Name"/>
-    <tableColumn id="12" name="Vol." dataDxfId="344"/>
-    <tableColumn id="22" name="Balance" dataDxfId="343">
+    <tableColumn id="12" name="Vol." dataDxfId="343"/>
+    <tableColumn id="22" name="Balance" dataDxfId="342">
       <calculatedColumnFormula>SUM(((Table168[[#This Row],[Avg DPS]]*(Table168[[#This Row],[Range]]))+(Table168[[#This Row],[Avg DPS]]*(Table168[[#This Row],[Arm Pen (%)]]/4)))/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Avg DPS" dataDxfId="342">
+    <tableColumn id="20" name="Avg DPS" dataDxfId="341">
       <calculatedColumnFormula>SUM(Table168[[#This Row],[DPS]]*Table168[[#This Row],[Avg Accuracy]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="341">
+    <tableColumn id="15" name="DPS" dataDxfId="340">
       <calculatedColumnFormula>SUM((Table168[[#This Row],[Damage]]*Table168[[#This Row],[Burst]])/(Table168[[#This Row],[Ranged Cooldown]]+Table168[[#This Row],[Warm-up]]+(Table168[[#This Row],[Burst Time]]*(Table168[[#This Row],[Burst]]-1))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" name="Range"/>
-    <tableColumn id="17" name="Avg Accuracy" dataDxfId="340">
+    <tableColumn id="17" name="Avg Accuracy" dataDxfId="339">
       <calculatedColumnFormula>SUM((Table168[[#This Row],[Accuracy (Close)]]+Table168[[#This Row],[Accuracy (Short)]]+Table168[[#This Row],[Accuracy (Medium)]]+Table168[[#This Row],[Accuracy (Long)]])/4)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" name="Damage"/>
@@ -5190,7 +5178,7 @@
     <tableColumn id="4" name="Ranged Cooldown"/>
     <tableColumn id="5" name="Warm-up"/>
     <tableColumn id="6" name="RPM"/>
-    <tableColumn id="7" name="Burst Time" dataDxfId="339">
+    <tableColumn id="7" name="Burst Time" dataDxfId="338">
       <calculatedColumnFormula>60/N4</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" name="Accuracy (Close)"/>
@@ -5200,7 +5188,7 @@
     <tableColumn id="13" name="Bullet Speed"/>
     <tableColumn id="14" name="Weight"/>
     <tableColumn id="21" name="Craftable"/>
-    <tableColumn id="23" name="Value" dataDxfId="338"/>
+    <tableColumn id="23" name="Value" dataDxfId="337"/>
     <tableColumn id="24" name="SoundShoot"/>
     <tableColumn id="25" name="SoundInteract"/>
   </tableColumns>
@@ -5219,18 +5207,18 @@
   </sortState>
   <tableColumns count="25">
     <tableColumn id="1" name="Weapon Name"/>
-    <tableColumn id="12" name="Vol." dataDxfId="318"/>
-    <tableColumn id="22" name="Balance" dataDxfId="317">
+    <tableColumn id="12" name="Vol." dataDxfId="317"/>
+    <tableColumn id="22" name="Balance" dataDxfId="316">
       <calculatedColumnFormula>SUM(((Table1614[[#This Row],[Avg DPS]]*(Table1614[[#This Row],[Range]]))+(Table1614[[#This Row],[Avg DPS]]*(Table1614[[#This Row],[Arm Pen (%)]]/4)))/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Avg DPS" dataDxfId="316">
+    <tableColumn id="20" name="Avg DPS" dataDxfId="315">
       <calculatedColumnFormula>SUM(Table1614[[#This Row],[DPS]]*Table1614[[#This Row],[Avg Accuracy]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="315">
+    <tableColumn id="15" name="DPS" dataDxfId="314">
       <calculatedColumnFormula>SUM((Table1614[[#This Row],[Damage]]*Table1614[[#This Row],[Burst]])/(Table1614[[#This Row],[Ranged Cooldown]]+Table1614[[#This Row],[Warm-up]]+(Table1614[[#This Row],[Burst Time]]*(Table1614[[#This Row],[Burst]]-1))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" name="Range"/>
-    <tableColumn id="17" name="Avg Accuracy" dataDxfId="314">
+    <tableColumn id="17" name="Avg Accuracy" dataDxfId="313">
       <calculatedColumnFormula>SUM((Table1614[[#This Row],[Accuracy (Close)]]+Table1614[[#This Row],[Accuracy (Short)]]+Table1614[[#This Row],[Accuracy (Medium)]]+Table1614[[#This Row],[Accuracy (Long)]])/4)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" name="Damage"/>
@@ -5240,7 +5228,7 @@
     <tableColumn id="4" name="Ranged Cooldown"/>
     <tableColumn id="5" name="Warm-up"/>
     <tableColumn id="6" name="RPM"/>
-    <tableColumn id="7" name="Burst Time" dataDxfId="313">
+    <tableColumn id="7" name="Burst Time" dataDxfId="312">
       <calculatedColumnFormula>60/N4</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" name="Accuracy (Close)"/>
@@ -5249,10 +5237,10 @@
     <tableColumn id="11" name="Accuracy (Long)"/>
     <tableColumn id="13" name="Bullet Speed"/>
     <tableColumn id="14" name="Weight"/>
-    <tableColumn id="21" name="Craftable" dataDxfId="312"/>
-    <tableColumn id="23" name="Value" dataDxfId="311"/>
-    <tableColumn id="24" name="SoundShoot" dataDxfId="310"/>
-    <tableColumn id="25" name="SoundInteract" dataDxfId="309"/>
+    <tableColumn id="21" name="Craftable" dataDxfId="311"/>
+    <tableColumn id="23" name="Value" dataDxfId="310"/>
+    <tableColumn id="24" name="SoundShoot" dataDxfId="309"/>
+    <tableColumn id="25" name="SoundInteract" dataDxfId="308"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5281,18 +5269,18 @@
   </sortState>
   <tableColumns count="25">
     <tableColumn id="1" name="Weapon Name"/>
-    <tableColumn id="12" name="Vol." dataDxfId="291"/>
-    <tableColumn id="22" name="Balance" dataDxfId="290">
+    <tableColumn id="12" name="Vol." dataDxfId="290"/>
+    <tableColumn id="22" name="Balance" dataDxfId="289">
       <calculatedColumnFormula>SUM(((Table16[[#This Row],[AC/DPS]]*(Table16[[#This Row],[Range]]))+(Table16[[#This Row],[AC/DPS]]*(Table16[[#This Row],[Arm Pen (%)]]/4)))/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="AC/DPS" dataDxfId="289">
+    <tableColumn id="20" name="AC/DPS" dataDxfId="288">
       <calculatedColumnFormula>SUM(Table16[[#This Row],[DPS]]*Table16[[#This Row],[Avg Accuracy]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="288">
+    <tableColumn id="15" name="DPS" dataDxfId="287">
       <calculatedColumnFormula>SUM((Table16[[#This Row],[Damage]]*Table16[[#This Row],[Burst]])/(Table16[[#This Row],[Ranged Cooldown]]+Table16[[#This Row],[Warm-up]]+(Table16[[#This Row],[Burst Time]]*(Table16[[#This Row],[Burst]]-1))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" name="Range"/>
-    <tableColumn id="17" name="Avg Accuracy" dataDxfId="287">
+    <tableColumn id="17" name="Avg Accuracy" dataDxfId="286">
       <calculatedColumnFormula>SUM((Table16[[#This Row],[Accuracy (Close)]]+Table16[[#This Row],[Accuracy (Short)]]+Table16[[#This Row],[Accuracy (Medium)]]+Table16[[#This Row],[Accuracy (Long)]])/4)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" name="Damage"/>
@@ -5302,7 +5290,7 @@
     <tableColumn id="4" name="Ranged Cooldown"/>
     <tableColumn id="5" name="Warm-up"/>
     <tableColumn id="6" name="RPM"/>
-    <tableColumn id="7" name="Burst Time" dataDxfId="286">
+    <tableColumn id="7" name="Burst Time" dataDxfId="285">
       <calculatedColumnFormula>60/N4</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" name="Accuracy (Close)"/>
@@ -5311,8 +5299,8 @@
     <tableColumn id="11" name="Accuracy (Long)"/>
     <tableColumn id="13" name="Bullet Speed"/>
     <tableColumn id="14" name="Weight"/>
-    <tableColumn id="21" name="Craftable" dataDxfId="285"/>
-    <tableColumn id="23" name="Value" dataDxfId="284"/>
+    <tableColumn id="21" name="Craftable" dataDxfId="284"/>
+    <tableColumn id="23" name="Value" dataDxfId="283"/>
     <tableColumn id="24" name="SoundShoot"/>
     <tableColumn id="25" name="SoundInteract"/>
   </tableColumns>
@@ -5349,27 +5337,27 @@
   <tableColumns count="30">
     <tableColumn id="1" name="Weapon Name"/>
     <tableColumn id="12" name="Vol."/>
-    <tableColumn id="22" name="Balance" dataDxfId="263">
+    <tableColumn id="22" name="Balance" dataDxfId="262">
       <calculatedColumnFormula>SUM(((Table16810[[#This Row],[Avg DPS]]*(Table16810[[#This Row],[Range]]))+(Table16810[[#This Row],[Avg DPS]]*(Table16810[[#This Row],[Arm Pen (%)]]/4)))/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Avg DPS" dataDxfId="262">
+    <tableColumn id="20" name="Avg DPS" dataDxfId="261">
       <calculatedColumnFormula>SUM(Table16810[[#This Row],[DPS]]*Table16810[[#This Row],[Avg Accuracy]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="261">
+    <tableColumn id="15" name="DPS" dataDxfId="260">
       <calculatedColumnFormula>SUM((Table16810[[#This Row],[Damage]]*Table16810[[#This Row],[Burst]])/(Table16810[[#This Row],[Ranged Cooldown]]+Table16810[[#This Row],[Warm-up]]+(Table16810[[#This Row],[Burst Time]]*(Table16810[[#This Row],[Burst]]-1))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" name="Range"/>
-    <tableColumn id="17" name="Avg Accuracy" dataDxfId="260">
+    <tableColumn id="17" name="Avg Accuracy" dataDxfId="259">
       <calculatedColumnFormula>SUM((Table16810[[#This Row],[Accuracy (Close)]]+Table16810[[#This Row],[Accuracy (Short)]]+Table16810[[#This Row],[Accuracy (Medium)]]+Table16810[[#This Row],[Accuracy (Long)]])/4)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" name="Damage"/>
     <tableColumn id="18" name="Stopping Pwr"/>
     <tableColumn id="19" name="Arm Pen (%)"/>
     <tableColumn id="3" name="Burst"/>
-    <tableColumn id="4" name="Ranged Cooldown" dataDxfId="259"/>
-    <tableColumn id="5" name="Warm-up" dataDxfId="258"/>
+    <tableColumn id="4" name="Ranged Cooldown" dataDxfId="258"/>
+    <tableColumn id="5" name="Warm-up" dataDxfId="257"/>
     <tableColumn id="6" name="RPM"/>
-    <tableColumn id="7" name="Burst Time" dataDxfId="257">
+    <tableColumn id="7" name="Burst Time" dataDxfId="256">
       <calculatedColumnFormula>60/N4</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" name="Accuracy (Close)"/>
@@ -5377,16 +5365,16 @@
     <tableColumn id="10" name="Accuracy (Medium)"/>
     <tableColumn id="11" name="Accuracy (Long)"/>
     <tableColumn id="13" name="Bullet Speed"/>
-    <tableColumn id="14" name="Weight" dataDxfId="256"/>
-    <tableColumn id="21" name="Craftable" dataDxfId="255"/>
+    <tableColumn id="14" name="Weight" dataDxfId="255"/>
+    <tableColumn id="21" name="Craftable" dataDxfId="254"/>
     <tableColumn id="23" name="Value"/>
-    <tableColumn id="27" name="SLP_M400THShot" dataDxfId="254"/>
-    <tableColumn id="30" name="SoundInteract" dataDxfId="253"/>
-    <tableColumn id="24" name="Special" dataDxfId="252"/>
-    <tableColumn id="28" name="S. Damage" dataDxfId="251"/>
-    <tableColumn id="25" name="S. Ammo" dataDxfId="250"/>
-    <tableColumn id="26" name="S. Range" dataDxfId="249"/>
-    <tableColumn id="29" name="S. Cost" dataDxfId="248"/>
+    <tableColumn id="27" name="SLP_M400THShot" dataDxfId="253"/>
+    <tableColumn id="30" name="SoundInteract" dataDxfId="252"/>
+    <tableColumn id="24" name="Special" dataDxfId="251"/>
+    <tableColumn id="28" name="S. Damage" dataDxfId="250"/>
+    <tableColumn id="25" name="S. Ammo" dataDxfId="249"/>
+    <tableColumn id="26" name="S. Range" dataDxfId="248"/>
+    <tableColumn id="29" name="S. Cost" dataDxfId="247"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5404,27 +5392,27 @@
   <tableColumns count="30">
     <tableColumn id="1" name="Weapon Name"/>
     <tableColumn id="12" name="Vol."/>
-    <tableColumn id="22" name="Balance" dataDxfId="227">
+    <tableColumn id="22" name="Balance" dataDxfId="226">
       <calculatedColumnFormula>SUM(((Table168107[[#This Row],[Avg DPS]]*(Table168107[[#This Row],[Range]]))+(Table168107[[#This Row],[Avg DPS]]*(Table168107[[#This Row],[Arm Pen (%)]]/4)))/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Avg DPS" dataDxfId="226">
+    <tableColumn id="20" name="Avg DPS" dataDxfId="225">
       <calculatedColumnFormula>SUM(Table168107[[#This Row],[DPS]]*Table168107[[#This Row],[Avg Accuracy]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="225">
+    <tableColumn id="15" name="DPS" dataDxfId="224">
       <calculatedColumnFormula>SUM((Table168107[[#This Row],[Damage]]*Table168107[[#This Row],[Burst]])/(Table168107[[#This Row],[Ranged Cooldown]]+Table168107[[#This Row],[Warm-up]]+(Table168107[[#This Row],[Burst Time]]*(Table168107[[#This Row],[Burst]]-1))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" name="Range"/>
-    <tableColumn id="17" name="Avg Accuracy" dataDxfId="224">
+    <tableColumn id="17" name="Avg Accuracy" dataDxfId="223">
       <calculatedColumnFormula>SUM((Table168107[[#This Row],[Accuracy (Close)]]+Table168107[[#This Row],[Accuracy (Short)]]+Table168107[[#This Row],[Accuracy (Medium)]]+Table168107[[#This Row],[Accuracy (Long)]])/4)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" name="Damage"/>
     <tableColumn id="18" name="Stopping Pwr"/>
     <tableColumn id="19" name="Arm Pen (%)"/>
     <tableColumn id="3" name="Burst"/>
-    <tableColumn id="4" name="Ranged Cooldown" dataDxfId="223"/>
-    <tableColumn id="5" name="Warm-up" dataDxfId="222"/>
+    <tableColumn id="4" name="Ranged Cooldown" dataDxfId="222"/>
+    <tableColumn id="5" name="Warm-up" dataDxfId="221"/>
     <tableColumn id="6" name="RPM"/>
-    <tableColumn id="7" name="Burst Time" dataDxfId="221">
+    <tableColumn id="7" name="Burst Time" dataDxfId="220">
       <calculatedColumnFormula>60/N4</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" name="Accuracy (Close)"/>
@@ -5432,16 +5420,16 @@
     <tableColumn id="10" name="Accuracy (Medium)"/>
     <tableColumn id="11" name="Accuracy (Long)"/>
     <tableColumn id="13" name="Bullet Speed"/>
-    <tableColumn id="14" name="Weight" dataDxfId="220"/>
-    <tableColumn id="21" name="Craftable" dataDxfId="219"/>
+    <tableColumn id="14" name="Weight" dataDxfId="219"/>
+    <tableColumn id="21" name="Craftable" dataDxfId="218"/>
     <tableColumn id="23" name="Value"/>
-    <tableColumn id="27" name="SoundShoot" dataDxfId="218"/>
-    <tableColumn id="30" name="SoundInteract" dataDxfId="217"/>
-    <tableColumn id="24" name="Special" dataDxfId="216"/>
-    <tableColumn id="28" name="S. Damage" dataDxfId="215"/>
-    <tableColumn id="25" name="S. Ammo" dataDxfId="214"/>
-    <tableColumn id="26" name="S. Range" dataDxfId="213"/>
-    <tableColumn id="29" name="S. Cost" dataDxfId="212"/>
+    <tableColumn id="27" name="SoundShoot" dataDxfId="217"/>
+    <tableColumn id="30" name="SoundInteract" dataDxfId="216"/>
+    <tableColumn id="24" name="Special" dataDxfId="215"/>
+    <tableColumn id="28" name="S. Damage" dataDxfId="214"/>
+    <tableColumn id="25" name="S. Ammo" dataDxfId="213"/>
+    <tableColumn id="26" name="S. Range" dataDxfId="212"/>
+    <tableColumn id="29" name="S. Cost" dataDxfId="211"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5471,17 +5459,17 @@
   <tableColumns count="25">
     <tableColumn id="1" name="Weapon Name"/>
     <tableColumn id="12" name="Vol."/>
-    <tableColumn id="22" name="Balance" dataDxfId="191">
+    <tableColumn id="22" name="Balance" dataDxfId="190">
       <calculatedColumnFormula>SUM(((Table1681011[[#This Row],[Avg DPS]]*(Table1681011[[#This Row],[Range]]))+(Table1681011[[#This Row],[Avg DPS]]*(Table1681011[[#This Row],[Arm Pen (%)]]/4)))/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Avg DPS" dataDxfId="190">
+    <tableColumn id="20" name="Avg DPS" dataDxfId="189">
       <calculatedColumnFormula>SUM(Table1681011[[#This Row],[DPS]]*Table1681011[[#This Row],[Avg Accuracy]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="189">
+    <tableColumn id="15" name="DPS" dataDxfId="188">
       <calculatedColumnFormula>SUM((Table1681011[[#This Row],[Damage]]*Table1681011[[#This Row],[Burst]])/(Table1681011[[#This Row],[Ranged Cooldown]]+Table1681011[[#This Row],[Warm-up]]+(Table1681011[[#This Row],[Burst Time]]*(Table1681011[[#This Row],[Burst]]-1))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" name="Range"/>
-    <tableColumn id="17" name="Avg Accuracy" dataDxfId="188">
+    <tableColumn id="17" name="Avg Accuracy" dataDxfId="187">
       <calculatedColumnFormula>SUM((Table1681011[[#This Row],[Accuracy (Close)]]+Table1681011[[#This Row],[Accuracy (Short)]]+Table1681011[[#This Row],[Accuracy (Medium)]]+Table1681011[[#This Row],[Accuracy (Long)]])/4)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" name="Damage"/>
@@ -5491,7 +5479,7 @@
     <tableColumn id="4" name="Ranged Cooldown"/>
     <tableColumn id="5" name="Warm-up"/>
     <tableColumn id="6" name="RPM"/>
-    <tableColumn id="7" name="Burst Time" dataDxfId="187">
+    <tableColumn id="7" name="Burst Time" dataDxfId="186">
       <calculatedColumnFormula>60/N4</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" name="Accuracy (Close)"/>
@@ -5501,7 +5489,7 @@
     <tableColumn id="13" name="Bullet Speed"/>
     <tableColumn id="14" name="Weight"/>
     <tableColumn id="21" name="Craftable"/>
-    <tableColumn id="23" name="Value" dataDxfId="186"/>
+    <tableColumn id="23" name="Value" dataDxfId="185"/>
     <tableColumn id="24" name="SoundShoot"/>
     <tableColumn id="25" name="SoundInteract"/>
   </tableColumns>
@@ -5530,17 +5518,17 @@
   <tableColumns count="25">
     <tableColumn id="1" name="Weapon Name"/>
     <tableColumn id="12" name="Vol."/>
-    <tableColumn id="22" name="Balance" dataDxfId="184">
+    <tableColumn id="22" name="Balance" dataDxfId="183">
       <calculatedColumnFormula>SUM(((Table1681015[[#This Row],[Avg DPS]]*(Table1681015[[#This Row],[Range]]))+(Table1681015[[#This Row],[Avg DPS]]*(Table1681015[[#This Row],[Arm Pen (%)]]/4)))/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Avg DPS" dataDxfId="183">
+    <tableColumn id="20" name="Avg DPS" dataDxfId="182">
       <calculatedColumnFormula>SUM(Table1681015[[#This Row],[DPS]]*Table1681015[[#This Row],[Avg Accuracy]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="182">
+    <tableColumn id="15" name="DPS" dataDxfId="181">
       <calculatedColumnFormula>SUM((Table1681015[[#This Row],[Damage]]*Table1681015[[#This Row],[Burst]])/(Table1681015[[#This Row],[Ranged Cooldown]]+Table1681015[[#This Row],[Warm-up]]+(Table1681015[[#This Row],[Burst Time]]*(Table1681015[[#This Row],[Burst]]-1))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" name="Range"/>
-    <tableColumn id="17" name="Avg Accuracy" dataDxfId="181">
+    <tableColumn id="17" name="Avg Accuracy" dataDxfId="180">
       <calculatedColumnFormula>SUM((Table1681015[[#This Row],[Accuracy (Close)]]+Table1681015[[#This Row],[Accuracy (Short)]]+Table1681015[[#This Row],[Accuracy (Medium)]]+Table1681015[[#This Row],[Accuracy (Long)]])/4)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" name="Damage"/>
@@ -5550,7 +5538,7 @@
     <tableColumn id="4" name="Ranged Cooldown"/>
     <tableColumn id="5" name="Warm-up"/>
     <tableColumn id="6" name="RPM"/>
-    <tableColumn id="7" name="Burst Time" dataDxfId="180">
+    <tableColumn id="7" name="Burst Time" dataDxfId="179">
       <calculatedColumnFormula>60/N4</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" name="Accuracy (Close)"/>
@@ -5592,17 +5580,17 @@
   <tableColumns count="25">
     <tableColumn id="1" name="Weapon Name"/>
     <tableColumn id="12" name="Vol."/>
-    <tableColumn id="22" name="Balance" dataDxfId="160">
+    <tableColumn id="22" name="Balance" dataDxfId="159">
       <calculatedColumnFormula>SUM(((Table168101112[[#This Row],[Avg DPS]]*(Table168101112[[#This Row],[Range]]))+(Table168101112[[#This Row],[Avg DPS]]*(Table168101112[[#This Row],[Arm Pen (%)]]/4)))/100)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" name="Avg DPS" dataDxfId="159">
+    <tableColumn id="20" name="Avg DPS" dataDxfId="158">
       <calculatedColumnFormula>SUM(Table168101112[[#This Row],[DPS]]*Table168101112[[#This Row],[Avg Accuracy]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" name="DPS" dataDxfId="158">
+    <tableColumn id="15" name="DPS" dataDxfId="157">
       <calculatedColumnFormula>SUM((Table168101112[[#This Row],[Damage]]*Table168101112[[#This Row],[Burst]])/(Table168101112[[#This Row],[Ranged Cooldown]]+Table168101112[[#This Row],[Warm-up]]+(Table168101112[[#This Row],[Burst Time]]*(Table168101112[[#This Row],[Burst]]-1))))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="16" name="Range"/>
-    <tableColumn id="17" name="Avg Accuracy" dataDxfId="157">
+    <tableColumn id="17" name="Avg Accuracy" dataDxfId="156">
       <calculatedColumnFormula>SUM((Table168101112[[#This Row],[Accuracy (Close)]]+Table168101112[[#This Row],[Accuracy (Short)]]+Table168101112[[#This Row],[Accuracy (Medium)]]+Table168101112[[#This Row],[Accuracy (Long)]])/4)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" name="Damage"/>
@@ -5612,7 +5600,7 @@
     <tableColumn id="4" name="Ranged Cooldown"/>
     <tableColumn id="5" name="Warm-up"/>
     <tableColumn id="6" name="RPM"/>
-    <tableColumn id="7" name="Burst Time" dataDxfId="156">
+    <tableColumn id="7" name="Burst Time" dataDxfId="155">
       <calculatedColumnFormula>60/N4</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" name="Accuracy (Close)"/>
@@ -5953,7 +5941,7 @@
         <v>70</v>
       </c>
       <c r="I1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J1" s="89"/>
       <c r="K1" s="89"/>
@@ -7786,7 +7774,7 @@
     </row>
     <row r="25" spans="1:25">
       <c r="A25" s="90" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B25" s="4">
         <v>4</v>
@@ -7860,10 +7848,10 @@
         <v>142.29993513513509</v>
       </c>
       <c r="X25" t="s">
+        <v>486</v>
+      </c>
+      <c r="Y25" t="s">
         <v>488</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="26" spans="1:25" s="70" customFormat="1">
@@ -8636,74 +8624,74 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C500">
-    <cfRule type="cellIs" dxfId="383" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="382" priority="17" operator="greaterThan">
       <formula>1.259</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:O1048576">
-    <cfRule type="cellIs" dxfId="382" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="381" priority="16" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G500">
-    <cfRule type="cellIs" dxfId="381" priority="4" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="380" priority="4" stopIfTrue="1" operator="between">
       <formula>0.47</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="380" priority="5" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="379" priority="5" stopIfTrue="1" operator="between">
       <formula>0.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="379" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="378" priority="6" operator="between">
       <formula>0.52</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="378" priority="10" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="377" priority="10" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.63</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="377" priority="11" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="376" priority="11" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.6</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="376" priority="12" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="375" priority="12" operator="greaterThanOrEqual">
       <formula>0.57</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F500">
-    <cfRule type="cellIs" dxfId="375" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="374" priority="9" operator="between">
       <formula>24.5</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F500">
-    <cfRule type="cellIs" dxfId="374" priority="7" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="373" priority="7" stopIfTrue="1" operator="between">
       <formula>22.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="373" priority="8" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="372" priority="8" stopIfTrue="1" operator="between">
       <formula>23.5</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E500">
-    <cfRule type="cellIs" dxfId="372" priority="1" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="371" priority="1" stopIfTrue="1" operator="between">
       <formula>6.69</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="371" priority="2" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="370" priority="2" stopIfTrue="1" operator="between">
       <formula>6.99</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="370" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="369" priority="3" operator="between">
       <formula>7.32</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="369" priority="13" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="368" priority="13" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>8.84</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="368" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="367" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>8.46</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="367" priority="15" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="366" priority="15" operator="greaterThanOrEqual">
       <formula>8.07</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8753,7 +8741,7 @@
         <v>68</v>
       </c>
       <c r="I1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J1" s="89"/>
       <c r="K1" s="89"/>
@@ -9028,7 +9016,7 @@
     </row>
     <row r="6" spans="1:25">
       <c r="A6" s="47" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B6" s="54">
         <v>2</v>
@@ -9184,15 +9172,15 @@
         <v>262.80879545454542</v>
       </c>
       <c r="X7" s="47" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="Y7" s="47" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8" spans="1:25">
       <c r="A8" s="47" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B8" s="54">
         <v>4</v>
@@ -9266,15 +9254,15 @@
         <v>272.7619578947369</v>
       </c>
       <c r="X8" s="47" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="Y8" s="47" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" spans="1:25" s="70" customFormat="1">
       <c r="A9" s="54" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B9" s="64">
         <v>4</v>
@@ -9348,7 +9336,7 @@
         <v>255.47912432432432</v>
       </c>
       <c r="X9" s="47" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Y9" s="47" t="s">
         <v>388</v>
@@ -9356,7 +9344,7 @@
     </row>
     <row r="10" spans="1:25">
       <c r="A10" s="54" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B10" s="54">
         <v>4</v>
@@ -9430,7 +9418,7 @@
         <v>231.31559999999999</v>
       </c>
       <c r="X10" s="47" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Y10" s="47" t="s">
         <v>388</v>
@@ -9875,96 +9863,96 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C500">
-    <cfRule type="cellIs" dxfId="155" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="154" priority="23" operator="greaterThan">
       <formula>1.259</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E500">
-    <cfRule type="cellIs" dxfId="154" priority="20" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="153" priority="20" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>9.63</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="21" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="152" priority="21" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>9.21</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="152" priority="22" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="151" priority="22" operator="greaterThanOrEqual">
       <formula>8.79</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="17" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="150" priority="17" stopIfTrue="1" operator="between">
       <formula>7.28</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="150" priority="18" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="149" priority="18" stopIfTrue="1" operator="between">
       <formula>7.61</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="19" operator="between">
+    <cfRule type="cellIs" dxfId="148" priority="19" operator="between">
       <formula>7.97</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F500">
-    <cfRule type="cellIs" dxfId="148" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="147" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>20.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="15" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="146" priority="15" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>19.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="146" priority="16" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="145" priority="16" operator="greaterThanOrEqual">
       <formula>17.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="145" priority="11" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="144" priority="11" stopIfTrue="1" operator="between">
       <formula>9.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="12" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="143" priority="12" stopIfTrue="1" operator="between">
       <formula>11.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="143" priority="13" operator="between">
+    <cfRule type="cellIs" dxfId="142" priority="13" operator="between">
       <formula>13.9</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G500">
-    <cfRule type="cellIs" dxfId="142" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="141" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.89</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="141" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="140" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.85</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="10" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="139" priority="10" operator="greaterThanOrEqual">
       <formula>0.81</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="139" priority="5" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="138" priority="5" stopIfTrue="1" operator="between">
       <formula>0.67</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="6" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="137" priority="6" stopIfTrue="1" operator="between">
       <formula>0.7</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="136" priority="7" operator="between">
       <formula>0.73</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:O7">
-    <cfRule type="cellIs" dxfId="136" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="4" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O10">
-    <cfRule type="cellIs" dxfId="135" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O11">
-    <cfRule type="cellIs" dxfId="134" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O8">
-    <cfRule type="cellIs" dxfId="133" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10014,7 +10002,7 @@
         <v>68</v>
       </c>
       <c r="I1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J1" s="89"/>
       <c r="K1" s="89"/>
@@ -10200,7 +10188,7 @@
         <v>375.19815041379303</v>
       </c>
       <c r="X4" s="47" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="Y4" s="47" t="s">
         <v>377</v>
@@ -10915,76 +10903,76 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C500">
-    <cfRule type="cellIs" dxfId="106" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="105" priority="21" operator="greaterThan">
       <formula>1.7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E500">
-    <cfRule type="cellIs" dxfId="105" priority="15" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="104" priority="15" stopIfTrue="1" operator="between">
       <formula>16.25</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="104" priority="16" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="103" priority="16" stopIfTrue="1" operator="between">
       <formula>16.99</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="103" priority="17" operator="between">
+    <cfRule type="cellIs" dxfId="102" priority="17" operator="between">
       <formula>17.8</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="18" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="101" priority="18" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>21.49</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="19" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="100" priority="19" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>20.56</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="20" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="99" priority="20" operator="greaterThanOrEqual">
       <formula>19.62</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F500">
-    <cfRule type="cellIs" dxfId="99" priority="9" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="98" priority="9" stopIfTrue="1" operator="between">
       <formula>6.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="10" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="97" priority="10" stopIfTrue="1" operator="between">
       <formula>8.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="96" priority="11" operator="between">
       <formula>10.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="12" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="95" priority="12" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>18.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="95" priority="13" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="94" priority="13" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>16.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="14" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="93" priority="14" operator="greaterThanOrEqual">
       <formula>14.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G500">
-    <cfRule type="cellIs" dxfId="93" priority="3" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="92" priority="3" stopIfTrue="1" operator="between">
       <formula>0.48</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="4" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="91" priority="4" stopIfTrue="1" operator="between">
       <formula>0.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="91" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="90" priority="5" operator="between">
       <formula>0.52</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="6" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="89" priority="6" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.63</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="7" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="88" priority="7" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.61</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="8" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="87" priority="8" operator="greaterThanOrEqual">
       <formula>0.58</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11030,7 +11018,7 @@
         <v>165</v>
       </c>
       <c r="H1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I1" s="89"/>
       <c r="J1" s="89"/>
@@ -11917,7 +11905,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C19">
-    <cfRule type="cellIs" dxfId="61" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="1" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11930,7 +11918,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ50"/>
+  <dimension ref="A1:AJ48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.28515625" customWidth="1"/>
@@ -12232,7 +12220,7 @@
         <v>0</v>
       </c>
       <c r="AF4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG4" t="s">
         <v>419</v>
@@ -12342,7 +12330,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG5" t="s">
         <v>420</v>
@@ -12453,7 +12441,7 @@
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AI6" s="12" t="s">
         <v>103</v>
@@ -12560,7 +12548,7 @@
         <v>0</v>
       </c>
       <c r="AF7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AI7" s="12" t="s">
         <v>103</v>
@@ -12666,7 +12654,7 @@
         <v>0</v>
       </c>
       <c r="AF8" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
@@ -12679,7 +12667,7 @@
     </row>
     <row r="9" spans="1:36">
       <c r="A9" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B9" s="33" t="s">
         <v>288</v>
@@ -12775,7 +12763,7 @@
         <v>0</v>
       </c>
       <c r="AF9" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AI9" s="12" t="s">
         <v>103</v>
@@ -12786,22 +12774,22 @@
     </row>
     <row r="10" spans="1:36">
       <c r="A10" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>288</v>
       </c>
       <c r="C10" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>4.3790117647058819</v>
+        <v>4.6526999999999994</v>
       </c>
       <c r="D10" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>7.341176470588235</v>
+        <v>7.8</v>
       </c>
       <c r="E10" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>15.058823529411764</v>
+        <v>16</v>
       </c>
       <c r="F10">
         <v>45.9</v>
@@ -12823,7 +12811,7 @@
         <v>2</v>
       </c>
       <c r="L10">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="M10">
         <v>0.5</v>
@@ -12873,7 +12861,7 @@
         <v>0.22222222222222221</v>
       </c>
       <c r="AC10" s="44" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AD10" s="44" t="s">
         <v>87</v>
@@ -12882,7 +12870,7 @@
         <v>0</v>
       </c>
       <c r="AF10" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AI10" s="12" t="s">
         <v>103</v>
@@ -12893,22 +12881,22 @@
     </row>
     <row r="11" spans="1:36">
       <c r="A11" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B11" s="33" t="s">
         <v>288</v>
       </c>
       <c r="C11" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>13.606112359550561</v>
+        <v>14.415999999999999</v>
       </c>
       <c r="D11" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>24.449438202247194</v>
+        <v>25.904761904761905</v>
       </c>
       <c r="E11" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>57.528089887640448</v>
+        <v>60.952380952380949</v>
       </c>
       <c r="F11">
         <v>41.9</v>
@@ -12930,7 +12918,7 @@
         <v>8</v>
       </c>
       <c r="L11">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="M11">
         <v>0.5</v>
@@ -12989,7 +12977,7 @@
         <v>0</v>
       </c>
       <c r="AF11" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AI11" s="12" t="s">
         <v>103</v>
@@ -13007,15 +12995,15 @@
       </c>
       <c r="C12" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>2.7221931818181817</v>
+        <v>2.9944124999999997</v>
       </c>
       <c r="D12" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>4.3977272727272725</v>
+        <v>4.8374999999999995</v>
       </c>
       <c r="E12" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>7.8181818181818183</v>
+        <v>8.6</v>
       </c>
       <c r="F12" s="7">
         <v>46.9</v>
@@ -13037,7 +13025,7 @@
         <v>1</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="M12">
         <v>0.5</v>
@@ -13070,7 +13058,7 @@
         <v>90</v>
       </c>
       <c r="W12">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="X12" s="33" t="s">
         <v>303</v>
@@ -13083,7 +13071,7 @@
       </c>
       <c r="AA12" s="2">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.25</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AC12" s="44" t="s">
         <v>321</v>
@@ -13095,7 +13083,7 @@
         <v>0</v>
       </c>
       <c r="AF12" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AI12" s="12" t="s">
         <v>103</v>
@@ -13113,15 +13101,15 @@
       </c>
       <c r="C13" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>2.7563461538461538</v>
+        <v>2.9860416666666669</v>
       </c>
       <c r="D13" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>4.2307692307692308</v>
+        <v>4.5833333333333339</v>
       </c>
       <c r="E13" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>7.6923076923076925</v>
+        <v>8.3333333333333339</v>
       </c>
       <c r="F13">
         <v>48.9</v>
@@ -13143,7 +13131,7 @@
         <v>1</v>
       </c>
       <c r="L13">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>1</v>
@@ -13176,7 +13164,7 @@
         <v>100</v>
       </c>
       <c r="W13">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="X13" s="33" t="s">
         <v>303</v>
@@ -13189,7 +13177,7 @@
       </c>
       <c r="AA13" s="2">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AC13" s="92" t="s">
         <v>326</v>
@@ -13201,7 +13189,7 @@
         <v>0</v>
       </c>
       <c r="AF13" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AI13" s="12">
         <v>1.9</v>
@@ -13211,7 +13199,7 @@
       </c>
     </row>
     <row r="14" spans="1:36">
-      <c r="A14" t="s">
+      <c r="A14" s="7" t="s">
         <v>427</v>
       </c>
       <c r="B14" s="33" t="s">
@@ -13219,105 +13207,106 @@
       </c>
       <c r="C14" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>2.8167895522388062</v>
-      </c>
-      <c r="D14" s="3">
+        <v>3.0543230769230769</v>
+      </c>
+      <c r="D14" s="9">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>4.2104477611940299</v>
-      </c>
-      <c r="E14" s="2">
+        <v>4.4653846153846155</v>
+      </c>
+      <c r="E14" s="8">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>7.7611940298507465</v>
-      </c>
-      <c r="F14">
-        <v>49.9</v>
-      </c>
-      <c r="G14" s="2">
+        <v>8.3076923076923084</v>
+      </c>
+      <c r="F14" s="7">
+        <v>50.9</v>
+      </c>
+      <c r="G14" s="8">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.54249999999999998</v>
-      </c>
-      <c r="H14">
-        <v>52</v>
-      </c>
-      <c r="I14">
+        <v>0.53749999999999998</v>
+      </c>
+      <c r="H14" s="7">
+        <v>54</v>
+      </c>
+      <c r="I14" s="7">
         <v>3</v>
       </c>
-      <c r="J14">
-        <v>68</v>
-      </c>
-      <c r="K14">
-        <v>1</v>
-      </c>
-      <c r="L14">
-        <v>5.7</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>5.7</v>
-      </c>
-      <c r="P14">
+      <c r="J14" s="7">
+        <v>70</v>
+      </c>
+      <c r="K14" s="7">
+        <v>1</v>
+      </c>
+      <c r="L14" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="M14" s="7">
+        <v>1</v>
+      </c>
+      <c r="N14" s="7">
+        <v>0</v>
+      </c>
+      <c r="O14" s="7">
+        <v>6</v>
+      </c>
+      <c r="P14" s="7">
         <v>0.2</v>
       </c>
-      <c r="Q14">
-        <v>0.37</v>
-      </c>
-      <c r="R14">
+      <c r="Q14" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="R14" s="7">
         <v>0.7</v>
       </c>
-      <c r="S14">
+      <c r="S14" s="7">
         <v>0.9</v>
       </c>
-      <c r="T14">
-        <v>11.9</v>
-      </c>
-      <c r="U14">
+      <c r="T14" s="7">
+        <v>12.9</v>
+      </c>
+      <c r="U14" s="7">
+        <v>140</v>
+      </c>
+      <c r="V14" s="7">
         <v>120</v>
       </c>
-      <c r="V14">
-        <v>110</v>
-      </c>
-      <c r="W14">
-        <v>60</v>
+      <c r="W14" s="7">
+        <v>50</v>
       </c>
       <c r="X14" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="Y14">
+      <c r="Y14" s="7">
         <v>10</v>
       </c>
-      <c r="Z14">
+      <c r="Z14" s="7">
         <v>10</v>
       </c>
       <c r="AA14" s="2">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.16666666666666666</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="AB14" s="7"/>
       <c r="AC14" s="92" t="s">
         <v>326</v>
       </c>
-      <c r="AD14" s="44" t="s">
+      <c r="AD14" s="52" t="s">
         <v>87</v>
       </c>
       <c r="AE14" s="44">
         <v>0</v>
       </c>
       <c r="AF14" t="s">
-        <v>433</v>
-      </c>
-      <c r="AI14" s="13">
-        <v>2.9</v>
-      </c>
-      <c r="AJ14" s="13">
-        <v>4.5</v>
+        <v>431</v>
+      </c>
+      <c r="AI14" s="12">
+        <v>3.9</v>
+      </c>
+      <c r="AJ14" s="12">
+        <v>5.5</v>
       </c>
     </row>
     <row r="15" spans="1:36">
-      <c r="A15" s="7" t="s">
+      <c r="A15" t="s">
         <v>428</v>
       </c>
       <c r="B15" s="33" t="s">
@@ -13325,177 +13314,176 @@
       </c>
       <c r="C15" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>2.8361571428571426</v>
-      </c>
-      <c r="D15" s="9">
+        <v>2.7955839999999994</v>
+      </c>
+      <c r="D15" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>4.1464285714285714</v>
-      </c>
-      <c r="E15" s="8">
+        <v>3.9709999999999996</v>
+      </c>
+      <c r="E15" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>7.7142857142857144</v>
-      </c>
-      <c r="F15" s="7">
-        <v>50.9</v>
-      </c>
-      <c r="G15" s="8">
+        <v>7.6</v>
+      </c>
+      <c r="F15">
+        <v>51.9</v>
+      </c>
+      <c r="G15" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.53749999999999998</v>
-      </c>
-      <c r="H15" s="7">
-        <v>54</v>
-      </c>
-      <c r="I15" s="7">
-        <v>3</v>
-      </c>
-      <c r="J15" s="7">
-        <v>70</v>
-      </c>
-      <c r="K15" s="7">
-        <v>1</v>
-      </c>
-      <c r="L15" s="7">
+        <v>0.52249999999999996</v>
+      </c>
+      <c r="H15">
+        <v>57</v>
+      </c>
+      <c r="I15">
+        <v>3.5</v>
+      </c>
+      <c r="J15">
+        <v>74</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
         <v>6</v>
       </c>
-      <c r="M15" s="7">
-        <v>1</v>
-      </c>
-      <c r="N15" s="7">
-        <v>0</v>
-      </c>
-      <c r="O15" s="7">
-        <v>6</v>
-      </c>
-      <c r="P15" s="7">
+      <c r="M15">
+        <v>1.5</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>6.5</v>
+      </c>
+      <c r="P15">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="R15" s="7">
+      <c r="Q15">
+        <v>0.32</v>
+      </c>
+      <c r="R15">
         <v>0.7</v>
       </c>
-      <c r="S15" s="7">
-        <v>0.9</v>
-      </c>
-      <c r="T15" s="7">
-        <v>12.9</v>
-      </c>
-      <c r="U15" s="7">
+      <c r="S15">
+        <v>0.87</v>
+      </c>
+      <c r="T15">
+        <v>13.9</v>
+      </c>
+      <c r="U15">
         <v>140</v>
       </c>
-      <c r="V15" s="7">
-        <v>120</v>
-      </c>
-      <c r="W15" s="7">
-        <v>70</v>
+      <c r="V15">
+        <v>140</v>
+      </c>
+      <c r="W15">
+        <v>45</v>
       </c>
       <c r="X15" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="Y15" s="7">
-        <v>10</v>
-      </c>
-      <c r="Z15" s="7">
-        <v>10</v>
+      <c r="Y15">
+        <v>6</v>
+      </c>
+      <c r="Z15">
+        <v>6</v>
       </c>
       <c r="AA15" s="2">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="AB15" s="7"/>
+        <v>0.13333333333333333</v>
+      </c>
       <c r="AC15" s="92" t="s">
         <v>326</v>
       </c>
-      <c r="AD15" s="52" t="s">
+      <c r="AD15" s="44" t="s">
         <v>87</v>
       </c>
       <c r="AE15" s="44">
         <v>0</v>
       </c>
       <c r="AF15" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AI15" s="12">
-        <v>3.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AJ15" s="12">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="16" spans="1:36">
       <c r="A16" t="s">
-        <v>429</v>
+        <v>481</v>
       </c>
       <c r="B16" s="33" t="s">
         <v>288</v>
       </c>
       <c r="C16" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>2.62086</v>
+        <v>5.83596</v>
       </c>
       <c r="D16" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>3.7228124999999999</v>
+        <v>7.54</v>
       </c>
       <c r="E16" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>7.125</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>51.9</v>
+        <v>54.9</v>
       </c>
       <c r="G16" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.52249999999999996</v>
+        <v>0.9425</v>
       </c>
       <c r="H16">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="I16">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J16">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="M16">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="N16">
         <v>0</v>
       </c>
       <c r="O16">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="Q16">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="R16">
         <v>0.7</v>
       </c>
       <c r="S16">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="T16">
-        <v>13.9</v>
+        <v>15.9</v>
       </c>
       <c r="U16">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="V16">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="W16">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="X16" s="33" t="s">
         <v>303</v>
@@ -13508,7 +13496,7 @@
       </c>
       <c r="AA16" s="2">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>7.1428571428571425E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="AC16" s="92" t="s">
         <v>326</v>
@@ -13520,307 +13508,310 @@
         <v>0</v>
       </c>
       <c r="AF16" t="s">
-        <v>433</v>
-      </c>
-      <c r="AI16" s="12">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="AJ16" s="12">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:36">
-      <c r="A17" t="s">
-        <v>430</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="C17" s="2">
+        <v>431</v>
+      </c>
+      <c r="AI16" s="94">
+        <v>7.9</v>
+      </c>
+      <c r="AJ16" s="94">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" s="54" customFormat="1">
+      <c r="A17" s="70" t="s">
+        <v>291</v>
+      </c>
+      <c r="B17" s="71" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="72">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>5.392352777777778</v>
-      </c>
-      <c r="D17" s="3">
+        <v>4.6118824228305195</v>
+      </c>
+      <c r="D17" s="72">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>7.2722222222222221</v>
-      </c>
-      <c r="E17" s="2">
+        <v>10.750308677926618</v>
+      </c>
+      <c r="E17" s="72">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>7.5555555555555554</v>
-      </c>
-      <c r="F17">
-        <v>53.9</v>
-      </c>
-      <c r="G17" s="2">
+        <v>19.907979033197439</v>
+      </c>
+      <c r="F17" s="70">
+        <v>32.9</v>
+      </c>
+      <c r="G17" s="72">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.96250000000000002</v>
-      </c>
-      <c r="H17">
-        <v>68</v>
-      </c>
-      <c r="I17">
-        <v>4</v>
-      </c>
-      <c r="J17">
-        <v>81</v>
-      </c>
-      <c r="K17">
-        <v>1</v>
-      </c>
-      <c r="L17">
-        <v>7</v>
-      </c>
-      <c r="M17">
+        <v>0.54</v>
+      </c>
+      <c r="H17" s="70">
+        <v>27</v>
+      </c>
+      <c r="I17" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="J17" s="70">
+        <v>40</v>
+      </c>
+      <c r="K17" s="70">
+        <v>3</v>
+      </c>
+      <c r="L17" s="70">
+        <v>3.5</v>
+      </c>
+      <c r="M17" s="70">
+        <v>0</v>
+      </c>
+      <c r="N17" s="70">
+        <v>211</v>
+      </c>
+      <c r="O17" s="72">
+        <f t="shared" ref="O17:O18" si="0">60/N17</f>
+        <v>0.28436018957345971</v>
+      </c>
+      <c r="P17" s="70">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="Q17" s="70">
+        <v>0.72</v>
+      </c>
+      <c r="R17" s="70">
+        <v>0.66</v>
+      </c>
+      <c r="S17" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="T17" s="70">
+        <v>8.9</v>
+      </c>
+      <c r="U17" s="70">
+        <v>88</v>
+      </c>
+      <c r="V17" s="70">
+        <v>100</v>
+      </c>
+      <c r="W17" s="70">
+        <v>180</v>
+      </c>
+      <c r="X17" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y17" s="70">
+        <v>90</v>
+      </c>
+      <c r="Z17" s="70">
+        <v>30</v>
+      </c>
+      <c r="AA17" s="91">
+        <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
+        <v>0.5</v>
+      </c>
+      <c r="AB17" s="70">
+        <v>1217</v>
+      </c>
+      <c r="AC17" s="79" t="s">
+        <v>293</v>
+      </c>
+      <c r="AD17" s="79" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE17" s="79">
+        <v>-150</v>
+      </c>
+      <c r="AF17" s="70" t="s">
+        <v>432</v>
+      </c>
+      <c r="AG17" s="70"/>
+      <c r="AH17" s="70"/>
+      <c r="AI17" s="71"/>
+      <c r="AJ17" s="71"/>
+    </row>
+    <row r="18" spans="1:36" s="54" customFormat="1">
+      <c r="A18" s="70" t="s">
+        <v>289</v>
+      </c>
+      <c r="B18" s="71" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="72">
+        <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
+        <v>0.87742702702702702</v>
+      </c>
+      <c r="D18" s="72">
+        <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
+        <v>2.6270270270270273</v>
+      </c>
+      <c r="E18" s="72">
+        <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
+        <v>4.8648648648648649</v>
+      </c>
+      <c r="F18" s="70">
+        <v>28.9</v>
+      </c>
+      <c r="G18" s="72">
+        <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
+        <v>0.54</v>
+      </c>
+      <c r="H18" s="70">
+        <v>12</v>
+      </c>
+      <c r="I18" s="70">
+        <v>0.5</v>
+      </c>
+      <c r="J18" s="70">
+        <v>18</v>
+      </c>
+      <c r="K18" s="70">
         <v>2</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>7</v>
-      </c>
-      <c r="P17">
-        <v>2</v>
-      </c>
-      <c r="Q17">
-        <v>0.3</v>
-      </c>
-      <c r="R17">
+      <c r="L18" s="70">
+        <v>4.8</v>
+      </c>
+      <c r="M18" s="70">
+        <v>0</v>
+      </c>
+      <c r="N18" s="70">
+        <v>450</v>
+      </c>
+      <c r="O18" s="72">
+        <f t="shared" si="0"/>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="P18" s="70">
+        <v>0.77</v>
+      </c>
+      <c r="Q18" s="70">
         <v>0.7</v>
       </c>
-      <c r="S17">
-        <v>0.85</v>
-      </c>
-      <c r="T17">
-        <v>14.9</v>
-      </c>
-      <c r="U17">
-        <v>160</v>
-      </c>
-      <c r="V17">
-        <v>180</v>
-      </c>
-      <c r="W17">
-        <v>90</v>
-      </c>
-      <c r="X17" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="Y17">
-        <v>5</v>
-      </c>
-      <c r="Z17">
-        <v>5</v>
-      </c>
-      <c r="AA17" s="2">
+      <c r="R18" s="70">
+        <v>0.45</v>
+      </c>
+      <c r="S18" s="70">
+        <v>0.24</v>
+      </c>
+      <c r="T18" s="70">
+        <v>0</v>
+      </c>
+      <c r="U18" s="70">
+        <v>70</v>
+      </c>
+      <c r="V18" s="70">
+        <v>13</v>
+      </c>
+      <c r="W18" s="70">
+        <v>80</v>
+      </c>
+      <c r="X18" s="71" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y18" s="70">
+        <v>60</v>
+      </c>
+      <c r="Z18" s="70">
+        <v>30</v>
+      </c>
+      <c r="AA18" s="91">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="AC17" s="92" t="s">
-        <v>326</v>
-      </c>
-      <c r="AD17" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE17" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>433</v>
-      </c>
-      <c r="AI17" s="12">
-        <v>5.9</v>
-      </c>
-      <c r="AJ17" s="12">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:36">
-      <c r="A18" t="s">
-        <v>483</v>
-      </c>
-      <c r="B18" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="C18" s="2">
-        <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>5.5580571428571419</v>
-      </c>
-      <c r="D18" s="3">
-        <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>7.1809523809523803</v>
-      </c>
-      <c r="E18" s="2">
-        <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>7.6190476190476186</v>
-      </c>
-      <c r="F18">
-        <v>54.9</v>
-      </c>
-      <c r="G18" s="2">
-        <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.9425</v>
-      </c>
-      <c r="H18">
-        <v>80</v>
-      </c>
-      <c r="I18">
-        <v>4</v>
-      </c>
-      <c r="J18">
-        <v>90</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18">
-        <v>8</v>
-      </c>
-      <c r="M18">
-        <v>2.5</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>8</v>
-      </c>
-      <c r="P18">
-        <v>2</v>
-      </c>
-      <c r="Q18">
-        <v>0.25</v>
-      </c>
-      <c r="R18">
-        <v>0.7</v>
-      </c>
-      <c r="S18">
-        <v>0.82</v>
-      </c>
-      <c r="T18">
-        <v>15.9</v>
-      </c>
-      <c r="U18">
-        <v>180</v>
-      </c>
-      <c r="V18">
-        <v>240</v>
-      </c>
-      <c r="W18">
-        <v>90</v>
-      </c>
-      <c r="X18" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="Y18">
-        <v>3</v>
-      </c>
-      <c r="Z18">
-        <v>3</v>
-      </c>
-      <c r="AA18" s="2">
-        <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="AC18" s="92" t="s">
-        <v>326</v>
-      </c>
-      <c r="AD18" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE18" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>433</v>
-      </c>
-      <c r="AI18" s="94">
-        <v>7.9</v>
-      </c>
-      <c r="AJ18" s="94">
-        <v>10.5</v>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="AB18" s="70">
+        <v>197</v>
+      </c>
+      <c r="AC18" s="79" t="s">
+        <v>306</v>
+      </c>
+      <c r="AD18" s="79" t="s">
+        <v>86</v>
+      </c>
+      <c r="AE18" s="79">
+        <v>-80</v>
+      </c>
+      <c r="AF18" s="70" t="s">
+        <v>432</v>
+      </c>
+      <c r="AG18" s="70"/>
+      <c r="AH18" s="70"/>
+      <c r="AI18" s="71"/>
+      <c r="AJ18" s="71"/>
     </row>
     <row r="19" spans="1:36" s="54" customFormat="1">
       <c r="A19" s="70" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B19" s="71" t="s">
         <v>35</v>
       </c>
       <c r="C19" s="72">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>4.6118824228305195</v>
+        <v>5.5350624999999987</v>
       </c>
       <c r="D19" s="72">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>10.750308677926618</v>
+        <v>8.3359375</v>
       </c>
       <c r="E19" s="72">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>19.907979033197439</v>
+        <v>17.1875</v>
       </c>
       <c r="F19" s="70">
-        <v>32.9</v>
+        <v>45.9</v>
       </c>
       <c r="G19" s="72">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.54</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="H19" s="70">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="I19" s="70">
         <v>0.5</v>
       </c>
       <c r="J19" s="70">
+        <v>82</v>
+      </c>
+      <c r="K19" s="70">
+        <v>1</v>
+      </c>
+      <c r="L19" s="70">
+        <v>3.2</v>
+      </c>
+      <c r="M19" s="70">
+        <v>0</v>
+      </c>
+      <c r="N19" s="70">
+        <v>0</v>
+      </c>
+      <c r="O19" s="72">
+        <v>3.2</v>
+      </c>
+      <c r="P19" s="70">
+        <v>0.22</v>
+      </c>
+      <c r="Q19" s="70">
+        <v>0.33</v>
+      </c>
+      <c r="R19" s="70">
+        <v>0.44</v>
+      </c>
+      <c r="S19" s="70">
+        <v>0.95</v>
+      </c>
+      <c r="T19" s="70">
+        <v>11.9</v>
+      </c>
+      <c r="U19" s="70">
+        <v>120</v>
+      </c>
+      <c r="V19" s="70">
         <v>40</v>
       </c>
-      <c r="K19" s="70">
-        <v>3</v>
-      </c>
-      <c r="L19" s="70">
-        <v>3.5</v>
-      </c>
-      <c r="M19" s="70">
-        <v>0</v>
-      </c>
-      <c r="N19" s="70">
-        <v>211</v>
-      </c>
-      <c r="O19" s="72">
-        <f t="shared" ref="O19:O20" si="0">60/N19</f>
-        <v>0.28436018957345971</v>
-      </c>
-      <c r="P19" s="70">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="Q19" s="70">
-        <v>0.72</v>
-      </c>
-      <c r="R19" s="70">
-        <v>0.66</v>
-      </c>
-      <c r="S19" s="70">
-        <v>0.5</v>
-      </c>
-      <c r="T19" s="70">
-        <v>8.9</v>
-      </c>
-      <c r="U19" s="70">
-        <v>88</v>
-      </c>
-      <c r="V19" s="70">
-        <v>100</v>
-      </c>
       <c r="W19" s="70">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="X19" s="71" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="Y19" s="70">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="Z19" s="70">
         <v>30</v>
@@ -13830,10 +13821,10 @@
         <v>0.5</v>
       </c>
       <c r="AB19" s="70">
-        <v>1217</v>
+        <v>1602</v>
       </c>
       <c r="AC19" s="79" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AD19" s="79" t="s">
         <v>87</v>
@@ -13842,330 +13833,335 @@
         <v>-150</v>
       </c>
       <c r="AF19" s="70" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG19" s="70"/>
       <c r="AH19" s="70"/>
       <c r="AI19" s="71"/>
       <c r="AJ19" s="71"/>
     </row>
-    <row r="20" spans="1:36" s="54" customFormat="1">
-      <c r="A20" s="70" t="s">
-        <v>289</v>
-      </c>
-      <c r="B20" s="71" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="72">
+    <row r="20" spans="1:36">
+      <c r="A20" s="14" t="s">
+        <v>470</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="C20" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>0.87742702702702702</v>
-      </c>
-      <c r="D20" s="72">
+        <v>4.0362839999999993</v>
+      </c>
+      <c r="D20" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>2.6270270270270273</v>
-      </c>
-      <c r="E20" s="72">
+        <v>9.5759999999999987</v>
+      </c>
+      <c r="E20" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>4.8648648648648649</v>
-      </c>
-      <c r="F20" s="70">
-        <v>28.9</v>
-      </c>
-      <c r="G20" s="72">
+        <v>20.16</v>
+      </c>
+      <c r="F20">
+        <v>35.9</v>
+      </c>
+      <c r="G20" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.54</v>
-      </c>
-      <c r="H20" s="70">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="H20">
+        <v>14</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>25</v>
+      </c>
+      <c r="K20">
+        <v>6</v>
+      </c>
+      <c r="L20">
+        <v>3.5</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>450</v>
+      </c>
+      <c r="O20" s="2">
+        <f>60/N20</f>
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="P20">
+        <v>0.4</v>
+      </c>
+      <c r="Q20">
+        <v>0.5</v>
+      </c>
+      <c r="R20">
+        <v>0.6</v>
+      </c>
+      <c r="S20">
+        <v>0.4</v>
+      </c>
+      <c r="T20">
+        <v>2.9</v>
+      </c>
+      <c r="U20">
+        <v>100</v>
+      </c>
+      <c r="V20">
+        <v>25</v>
+      </c>
+      <c r="W20">
+        <v>100</v>
+      </c>
+      <c r="X20" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y20">
+        <v>240</v>
+      </c>
+      <c r="Z20">
+        <v>40</v>
+      </c>
+      <c r="AA20" s="2">
+        <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
+        <v>2.4</v>
+      </c>
+      <c r="AC20" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="AD20" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE20" s="44">
+        <v>-100</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>432</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>420</v>
+      </c>
+      <c r="AI20" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ20" s="12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36">
+      <c r="A21" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="C21" s="2">
+        <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
+        <v>5.341356687898088</v>
+      </c>
+      <c r="D21" s="3">
+        <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
+        <v>13.643312101910828</v>
+      </c>
+      <c r="E21" s="2">
+        <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
+        <v>32.101910828025474</v>
+      </c>
+      <c r="F21">
+        <v>32.9</v>
+      </c>
+      <c r="G21" s="2">
+        <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
+        <v>0.42500000000000004</v>
+      </c>
+      <c r="H21">
+        <v>14</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>25</v>
+      </c>
+      <c r="K21">
         <v>12</v>
       </c>
-      <c r="I20" s="70">
-        <v>0.5</v>
-      </c>
-      <c r="J20" s="70">
-        <v>18</v>
-      </c>
-      <c r="K20" s="70">
-        <v>2</v>
-      </c>
-      <c r="L20" s="70">
-        <v>4.8</v>
-      </c>
-      <c r="M20" s="70">
-        <v>0</v>
-      </c>
-      <c r="N20" s="70">
-        <v>450</v>
-      </c>
-      <c r="O20" s="72">
-        <f t="shared" si="0"/>
-        <v>0.13333333333333333</v>
-      </c>
-      <c r="P20" s="70">
-        <v>0.77</v>
-      </c>
-      <c r="Q20" s="70">
-        <v>0.7</v>
-      </c>
-      <c r="R20" s="70">
+      <c r="L21">
+        <v>4.5</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>900</v>
+      </c>
+      <c r="O21" s="2">
+        <f>60/N21</f>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="P21">
+        <v>0.35</v>
+      </c>
+      <c r="Q21">
         <v>0.45</v>
       </c>
-      <c r="S20" s="70">
-        <v>0.24</v>
-      </c>
-      <c r="T20" s="70">
-        <v>0</v>
-      </c>
-      <c r="U20" s="70">
-        <v>70</v>
-      </c>
-      <c r="V20" s="70">
-        <v>13</v>
-      </c>
-      <c r="W20" s="70">
-        <v>80</v>
-      </c>
-      <c r="X20" s="71" t="s">
+      <c r="R21">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="S21">
+        <v>0.35</v>
+      </c>
+      <c r="T21">
+        <v>3.9</v>
+      </c>
+      <c r="U21">
+        <v>100</v>
+      </c>
+      <c r="V21">
+        <v>45</v>
+      </c>
+      <c r="W21">
+        <v>100</v>
+      </c>
+      <c r="X21" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="Y20" s="70">
-        <v>60</v>
-      </c>
-      <c r="Z20" s="70">
-        <v>30</v>
-      </c>
-      <c r="AA20" s="91">
+      <c r="Y21">
+        <v>240</v>
+      </c>
+      <c r="Z21">
+        <v>20</v>
+      </c>
+      <c r="AA21" s="2">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.75</v>
-      </c>
-      <c r="AB20" s="70">
-        <v>197</v>
-      </c>
-      <c r="AC20" s="79" t="s">
-        <v>306</v>
-      </c>
-      <c r="AD20" s="79" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE20" s="79">
-        <v>-80</v>
-      </c>
-      <c r="AF20" s="70" t="s">
-        <v>434</v>
-      </c>
-      <c r="AG20" s="70"/>
-      <c r="AH20" s="70"/>
-      <c r="AI20" s="71"/>
-      <c r="AJ20" s="71"/>
-    </row>
-    <row r="21" spans="1:36" s="54" customFormat="1">
-      <c r="A21" s="70" t="s">
-        <v>296</v>
-      </c>
-      <c r="B21" s="71" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="72">
-        <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>5.5350624999999987</v>
-      </c>
-      <c r="D21" s="72">
-        <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>8.3359375</v>
-      </c>
-      <c r="E21" s="72">
-        <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>17.1875</v>
-      </c>
-      <c r="F21" s="70">
-        <v>45.9</v>
-      </c>
-      <c r="G21" s="72">
-        <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.48499999999999999</v>
-      </c>
-      <c r="H21" s="70">
-        <v>55</v>
-      </c>
-      <c r="I21" s="70">
-        <v>0.5</v>
-      </c>
-      <c r="J21" s="70">
-        <v>82</v>
-      </c>
-      <c r="K21" s="70">
-        <v>1</v>
-      </c>
-      <c r="L21" s="70">
-        <v>3.2</v>
-      </c>
-      <c r="M21" s="70">
-        <v>0</v>
-      </c>
-      <c r="N21" s="70">
-        <v>0</v>
-      </c>
-      <c r="O21" s="72">
-        <v>3.2</v>
-      </c>
-      <c r="P21" s="70">
-        <v>0.22</v>
-      </c>
-      <c r="Q21" s="70">
-        <v>0.33</v>
-      </c>
-      <c r="R21" s="70">
-        <v>0.44</v>
-      </c>
-      <c r="S21" s="70">
-        <v>0.95</v>
-      </c>
-      <c r="T21" s="70">
-        <v>11.9</v>
-      </c>
-      <c r="U21" s="70">
-        <v>120</v>
-      </c>
-      <c r="V21" s="70">
-        <v>40</v>
-      </c>
-      <c r="W21" s="70">
-        <v>60</v>
-      </c>
-      <c r="X21" s="71" t="s">
-        <v>322</v>
-      </c>
-      <c r="Y21" s="70">
-        <v>30</v>
-      </c>
-      <c r="Z21" s="70">
-        <v>30</v>
-      </c>
-      <c r="AA21" s="91">
-        <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.5</v>
-      </c>
-      <c r="AB21" s="70">
-        <v>1602</v>
-      </c>
-      <c r="AC21" s="79" t="s">
-        <v>297</v>
-      </c>
-      <c r="AD21" s="79" t="s">
+        <v>2.4</v>
+      </c>
+      <c r="AC21" s="44" t="s">
+        <v>318</v>
+      </c>
+      <c r="AD21" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="AE21" s="79">
-        <v>-150</v>
-      </c>
-      <c r="AF21" s="70" t="s">
-        <v>434</v>
-      </c>
-      <c r="AG21" s="70"/>
-      <c r="AH21" s="70"/>
-      <c r="AI21" s="71"/>
-      <c r="AJ21" s="71"/>
+      <c r="AE21" s="44">
+        <v>-100</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>432</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>420</v>
+      </c>
+      <c r="AI21" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ21" s="12" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="22" spans="1:36">
-      <c r="A22" s="14" t="s">
-        <v>472</v>
-      </c>
-      <c r="B22" s="12" t="s">
+      <c r="A22" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B22" s="33" t="s">
         <v>288</v>
       </c>
       <c r="C22" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>4.0362839999999993</v>
+        <v>10.352013422818793</v>
       </c>
       <c r="D22" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>9.5759999999999987</v>
+        <v>30.536912751677853</v>
       </c>
       <c r="E22" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>20.16</v>
+        <v>93.959731543624159</v>
       </c>
       <c r="F22">
-        <v>35.9</v>
+        <v>30.9</v>
       </c>
       <c r="G22" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.47499999999999998</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="H22">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J22">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="L22">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="M22">
         <v>0</v>
       </c>
       <c r="N22">
-        <v>450</v>
+        <v>1200</v>
       </c>
       <c r="O22" s="2">
         <f>60/N22</f>
-        <v>0.13333333333333333</v>
+        <v>0.05</v>
       </c>
       <c r="P22">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="Q22">
-        <v>0.5</v>
+        <v>0.34</v>
       </c>
       <c r="R22">
-        <v>0.6</v>
+        <v>0.49</v>
       </c>
       <c r="S22">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="T22">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="U22">
+        <v>70</v>
+      </c>
+      <c r="V22">
         <v>100</v>
       </c>
-      <c r="V22">
-        <v>25</v>
-      </c>
       <c r="W22">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="X22" s="33" t="s">
         <v>302</v>
       </c>
       <c r="Y22">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="Z22">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AA22" s="2">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC22" s="44" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AD22" s="44" t="s">
         <v>87</v>
       </c>
       <c r="AE22" s="44">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AF22" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG22" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AI22" s="12" t="s">
         <v>103</v>
@@ -14174,109 +14170,107 @@
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:36">
-      <c r="A23" s="1" t="s">
-        <v>473</v>
+    <row r="23" spans="1:36" s="54" customFormat="1">
+      <c r="A23" t="s">
+        <v>311</v>
       </c>
       <c r="B23" s="33" t="s">
         <v>288</v>
       </c>
       <c r="C23" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>5.341356687898088</v>
+        <v>1.7950000000000004</v>
       </c>
       <c r="D23" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>13.643312101910828</v>
+        <v>5.0000000000000009</v>
       </c>
       <c r="E23" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>32.101910828025474</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="F23">
-        <v>32.9</v>
+        <v>35.9</v>
       </c>
       <c r="G23" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.42500000000000004</v>
+        <v>0.75000000000000011</v>
       </c>
       <c r="H23">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J23">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L23">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
       <c r="N23">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2">
-        <f>60/N23</f>
-        <v>6.6666666666666666E-2</v>
+        <v>2.4</v>
       </c>
       <c r="P23">
-        <v>0.35</v>
+        <v>0.9</v>
       </c>
       <c r="Q23">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
       <c r="R23">
-        <v>0.55000000000000004</v>
+        <v>0.7</v>
       </c>
       <c r="S23">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="T23">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="U23">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="V23">
-        <v>45</v>
-      </c>
-      <c r="W23">
-        <v>100</v>
+        <v>40</v>
+      </c>
+      <c r="W23" s="33" t="s">
+        <v>103</v>
       </c>
       <c r="X23" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Y23">
-        <v>240</v>
-      </c>
-      <c r="Z23">
-        <v>20</v>
+        <v>103</v>
+      </c>
+      <c r="Y23" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z23" s="33" t="s">
+        <v>103</v>
       </c>
       <c r="AA23" s="2">
-        <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>2.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB23"/>
       <c r="AC23" s="44" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="AD23" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AE23" s="44">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AF23" t="s">
-        <v>434</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>420</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="AG23"/>
+      <c r="AH23"/>
       <c r="AI23" s="12" t="s">
         <v>103</v>
       </c>
@@ -14286,106 +14280,101 @@
     </row>
     <row r="24" spans="1:36">
       <c r="A24" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="B24" s="33" t="s">
         <v>288</v>
       </c>
       <c r="C24" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>10.352013422818793</v>
+        <v>2.17</v>
       </c>
       <c r="D24" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>30.536912751677853</v>
+        <v>5</v>
       </c>
       <c r="E24" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>93.959731543624159</v>
+        <v>8</v>
       </c>
       <c r="F24">
-        <v>30.9</v>
+        <v>40.9</v>
       </c>
       <c r="G24" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.32500000000000001</v>
+        <v>0.625</v>
       </c>
       <c r="H24">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I24">
         <v>0.5</v>
       </c>
       <c r="J24">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="O24" s="2">
-        <f>60/N24</f>
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="P24">
-        <v>0.22</v>
+        <v>0.85</v>
       </c>
       <c r="Q24">
-        <v>0.34</v>
+        <v>0.75</v>
       </c>
       <c r="R24">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="S24">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="T24">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="U24">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="V24">
-        <v>100</v>
-      </c>
-      <c r="W24">
-        <v>200</v>
+        <v>50</v>
+      </c>
+      <c r="W24" s="33" t="s">
+        <v>103</v>
       </c>
       <c r="X24" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="Y24">
-        <v>700</v>
-      </c>
-      <c r="Z24">
-        <v>10</v>
+        <v>103</v>
+      </c>
+      <c r="Y24" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z24" s="33" t="s">
+        <v>103</v>
       </c>
       <c r="AA24" s="2">
-        <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>3.5</v>
-      </c>
-      <c r="AC24" s="44" t="s">
-        <v>319</v>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="92" t="s">
+        <v>326</v>
       </c>
       <c r="AD24" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AE24" s="44">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="s">
-        <v>434</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="AI24" s="12" t="s">
         <v>103</v>
@@ -14394,107 +14383,106 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:36" s="54" customFormat="1">
+    <row r="25" spans="1:36">
       <c r="A25" t="s">
-        <v>311</v>
+        <v>472</v>
       </c>
       <c r="B25" s="33" t="s">
         <v>288</v>
       </c>
       <c r="C25" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>1.7950000000000004</v>
+        <v>4.7219538461538484</v>
       </c>
       <c r="D25" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>5.0000000000000009</v>
+        <v>9.2769230769230795</v>
       </c>
       <c r="E25" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>6.666666666666667</v>
+        <v>18.461538461538463</v>
       </c>
       <c r="F25">
-        <v>35.9</v>
+        <v>40.9</v>
       </c>
       <c r="G25" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.75000000000000011</v>
+        <v>0.50250000000000006</v>
       </c>
       <c r="H25">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L25">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O25" s="2">
-        <v>2.4</v>
+        <f t="shared" ref="O25:O26" si="1">60/N25</f>
+        <v>0.2</v>
       </c>
       <c r="P25">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="Q25">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="R25">
-        <v>0.7</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="S25">
+        <v>0.43</v>
+      </c>
+      <c r="T25">
+        <v>5.9</v>
+      </c>
+      <c r="U25">
+        <v>100</v>
+      </c>
+      <c r="V25">
+        <v>55</v>
+      </c>
+      <c r="W25">
+        <v>100</v>
+      </c>
+      <c r="X25" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y25">
+        <v>60</v>
+      </c>
+      <c r="Z25">
+        <v>20</v>
+      </c>
+      <c r="AA25" s="2">
+        <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
         <v>0.6</v>
       </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>65</v>
-      </c>
-      <c r="V25">
-        <v>40</v>
-      </c>
-      <c r="W25" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="X25" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y25" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z25" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA25" s="2">
-        <v>0</v>
-      </c>
-      <c r="AB25"/>
       <c r="AC25" s="44" t="s">
-        <v>312</v>
+        <v>483</v>
       </c>
       <c r="AD25" s="44" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AE25" s="44">
-        <v>-200</v>
+        <v>-150</v>
       </c>
       <c r="AF25" t="s">
-        <v>434</v>
-      </c>
-      <c r="AG25"/>
-      <c r="AH25"/>
+        <v>432</v>
+      </c>
       <c r="AI25" s="12" t="s">
         <v>103</v>
       </c>
@@ -14502,104 +14490,109 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:36">
-      <c r="A26" t="s">
-        <v>482</v>
+    <row r="26" spans="1:36" s="93" customFormat="1">
+      <c r="A26" s="7" t="s">
+        <v>473</v>
       </c>
       <c r="B26" s="33" t="s">
         <v>288</v>
       </c>
       <c r="C26" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>2.17</v>
+        <v>4.9317030000000015</v>
       </c>
       <c r="D26" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>5</v>
+        <v>8.8620000000000019</v>
       </c>
       <c r="E26" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>8</v>
-      </c>
-      <c r="F26">
-        <v>40.9</v>
+        <v>16.8</v>
+      </c>
+      <c r="F26" s="7">
+        <v>41.9</v>
       </c>
       <c r="G26" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.625</v>
-      </c>
-      <c r="H26">
-        <v>24</v>
-      </c>
-      <c r="I26">
+        <v>0.52750000000000008</v>
+      </c>
+      <c r="H26" s="7">
+        <v>28</v>
+      </c>
+      <c r="I26" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="J26" s="7">
+        <v>55</v>
+      </c>
+      <c r="K26" s="7">
+        <v>3</v>
+      </c>
+      <c r="L26" s="7">
+        <v>4</v>
+      </c>
+      <c r="M26" s="7">
+        <v>0</v>
+      </c>
+      <c r="N26" s="7">
+        <v>120</v>
+      </c>
+      <c r="O26" s="2">
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="J26">
-        <v>10</v>
-      </c>
-      <c r="K26">
-        <v>1</v>
-      </c>
-      <c r="L26">
-        <v>3</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" s="2">
-        <v>3</v>
-      </c>
-      <c r="P26">
-        <v>0.85</v>
-      </c>
-      <c r="Q26">
-        <v>0.75</v>
-      </c>
-      <c r="R26">
-        <v>0.5</v>
-      </c>
-      <c r="S26">
+      <c r="P26" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="R26" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="S26" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T26">
+        <v>5.9</v>
+      </c>
+      <c r="U26" s="7">
+        <v>100</v>
+      </c>
+      <c r="V26" s="7">
+        <v>65</v>
+      </c>
+      <c r="W26" s="7">
+        <v>100</v>
+      </c>
+      <c r="X26" s="37" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y26" s="7">
+        <v>40</v>
+      </c>
+      <c r="Z26" s="7">
+        <v>40</v>
+      </c>
+      <c r="AA26" s="2">
+        <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
         <v>0.4</v>
       </c>
-      <c r="T26">
-        <v>2.9</v>
-      </c>
-      <c r="U26">
-        <v>90</v>
-      </c>
-      <c r="V26">
-        <v>50</v>
-      </c>
-      <c r="W26" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="X26" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y26" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z26" s="33" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA26" s="2">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="92" t="s">
-        <v>326</v>
-      </c>
-      <c r="AD26" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE26" s="44">
-        <v>0</v>
+      <c r="AB26" s="7"/>
+      <c r="AC26" s="44" t="s">
+        <v>484</v>
+      </c>
+      <c r="AD26" s="52" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE26" s="52">
+        <v>-200</v>
       </c>
       <c r="AF26" t="s">
-        <v>434</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="AG26" s="51"/>
+      <c r="AH26" s="51"/>
       <c r="AI26" s="12" t="s">
         <v>103</v>
       </c>
@@ -14616,59 +14609,59 @@
       </c>
       <c r="C27" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>4.7219538461538484</v>
+        <v>3.8756413793103452</v>
       </c>
       <c r="D27" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>9.2769230769230795</v>
+        <v>6.8413793103448279</v>
       </c>
       <c r="E27" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>18.461538461538463</v>
+        <v>14.712643678160921</v>
       </c>
       <c r="F27">
-        <v>40.9</v>
+        <v>42.9</v>
       </c>
       <c r="G27" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.50250000000000006</v>
+        <v>0.46499999999999997</v>
       </c>
       <c r="H27">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L27">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
       <c r="N27">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="O27" s="2">
-        <f t="shared" ref="O27:O28" si="1">60/N27</f>
+        <f t="shared" ref="O27:O40" si="2">60/N27</f>
+        <v>0.1</v>
+      </c>
+      <c r="P27">
         <v>0.2</v>
       </c>
-      <c r="P27">
-        <v>0.3</v>
-      </c>
       <c r="Q27">
-        <v>0.7</v>
+        <v>0.51</v>
       </c>
       <c r="R27">
-        <v>0.57999999999999996</v>
+        <v>0.67</v>
       </c>
       <c r="S27">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="T27">
         <v>5.9</v>
@@ -14677,45 +14670,45 @@
         <v>100</v>
       </c>
       <c r="V27">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="W27">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="X27" s="33" t="s">
         <v>302</v>
       </c>
       <c r="Y27">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Z27">
         <v>20</v>
       </c>
       <c r="AA27" s="2">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.6</v>
-      </c>
-      <c r="AC27" s="44" t="s">
-        <v>485</v>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="AC27" s="92" t="s">
+        <v>326</v>
       </c>
       <c r="AD27" s="44" t="s">
         <v>87</v>
       </c>
       <c r="AE27" s="44">
-        <v>-150</v>
+        <v>-200</v>
       </c>
       <c r="AF27" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AI27" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="AJ27" s="12" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28" spans="1:36" s="93" customFormat="1">
-      <c r="A28" s="7" t="s">
+      <c r="AJ27" s="12">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36">
+      <c r="A28" t="s">
         <v>475</v>
       </c>
       <c r="B28" s="33" t="s">
@@ -14723,100 +14716,97 @@
       </c>
       <c r="C28" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>4.9317030000000015</v>
+        <v>10.51895172413793</v>
       </c>
       <c r="D28" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>8.8620000000000019</v>
+        <v>21.186206896551724</v>
       </c>
       <c r="E28" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>16.8</v>
-      </c>
-      <c r="F28" s="7">
-        <v>41.9</v>
+        <v>52.965517241379317</v>
+      </c>
+      <c r="F28">
+        <v>35.9</v>
       </c>
       <c r="G28" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.52750000000000008</v>
-      </c>
-      <c r="H28" s="7">
-        <v>28</v>
-      </c>
-      <c r="I28" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="J28" s="7">
+        <v>0.39999999999999997</v>
+      </c>
+      <c r="H28">
+        <v>32</v>
+      </c>
+      <c r="I28">
+        <v>2</v>
+      </c>
+      <c r="J28">
         <v>55</v>
       </c>
-      <c r="K28" s="7">
-        <v>3</v>
-      </c>
-      <c r="L28" s="7">
-        <v>4</v>
-      </c>
-      <c r="M28" s="7">
-        <v>0</v>
-      </c>
-      <c r="N28" s="7">
-        <v>120</v>
+      <c r="K28">
+        <v>8</v>
+      </c>
+      <c r="L28">
+        <v>4.25</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>720</v>
       </c>
       <c r="O28" s="2">
-        <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-      <c r="P28" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="Q28" s="7">
-        <v>0.6</v>
-      </c>
-      <c r="R28" s="7">
-        <v>0.71</v>
-      </c>
-      <c r="S28" s="7">
-        <v>0.55000000000000004</v>
+        <f t="shared" si="2"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="P28">
+        <v>0.2</v>
+      </c>
+      <c r="Q28">
+        <v>0.47</v>
+      </c>
+      <c r="R28">
+        <v>0.61</v>
+      </c>
+      <c r="S28">
+        <v>0.32</v>
       </c>
       <c r="T28">
         <v>5.9</v>
       </c>
-      <c r="U28" s="7">
+      <c r="U28">
         <v>100</v>
       </c>
-      <c r="V28" s="7">
-        <v>65</v>
-      </c>
-      <c r="W28" s="7">
-        <v>100</v>
-      </c>
-      <c r="X28" s="37" t="s">
+      <c r="V28">
+        <v>115</v>
+      </c>
+      <c r="W28">
+        <v>180</v>
+      </c>
+      <c r="X28" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="Y28" s="7">
+      <c r="Y28">
         <v>40</v>
       </c>
-      <c r="Z28" s="7">
-        <v>40</v>
+      <c r="Z28">
+        <v>5</v>
       </c>
       <c r="AA28" s="2">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.4</v>
-      </c>
-      <c r="AB28" s="7"/>
-      <c r="AC28" s="44" t="s">
-        <v>486</v>
-      </c>
-      <c r="AD28" s="52" t="s">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="AC28" s="92" t="s">
+        <v>326</v>
+      </c>
+      <c r="AD28" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="AE28" s="52">
+      <c r="AE28" s="44">
         <v>-200</v>
       </c>
       <c r="AF28" t="s">
-        <v>434</v>
-      </c>
-      <c r="AG28" s="51"/>
-      <c r="AH28" s="51"/>
+        <v>432</v>
+      </c>
       <c r="AI28" s="12" t="s">
         <v>103</v>
       </c>
@@ -14833,84 +14823,83 @@
       </c>
       <c r="C29" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>3.8756413793103452</v>
+        <v>2.3568300000000004</v>
       </c>
       <c r="D29" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>6.8413793103448279</v>
+        <v>3.87</v>
       </c>
       <c r="E29" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>14.712643678160921</v>
+        <v>6.88</v>
       </c>
       <c r="F29">
-        <v>42.9</v>
+        <v>45.9</v>
       </c>
       <c r="G29" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.46499999999999997</v>
+        <v>0.5625</v>
       </c>
       <c r="H29">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="I29">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J29">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L29">
-        <v>4.25</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N29">
-        <v>600</v>
-      </c>
-      <c r="O29" s="2">
-        <f t="shared" ref="O29:O42" si="2">60/N29</f>
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>6</v>
       </c>
       <c r="P29">
         <v>0.2</v>
       </c>
       <c r="Q29">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
       <c r="R29">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="S29">
-        <v>0.48</v>
+        <v>0.95</v>
       </c>
       <c r="T29">
-        <v>5.9</v>
+        <v>9.9</v>
       </c>
       <c r="U29">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="V29">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="W29">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="X29" s="33" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Y29">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AA29" s="2">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.22222222222222221</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AC29" s="92" t="s">
         <v>326</v>
@@ -14919,16 +14908,16 @@
         <v>87</v>
       </c>
       <c r="AE29" s="44">
-        <v>-200</v>
+        <v>-250</v>
       </c>
       <c r="AF29" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AI29" s="12" t="s">
         <v>103</v>
       </c>
       <c r="AJ29" s="12">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30" spans="1:36">
@@ -14940,84 +14929,83 @@
       </c>
       <c r="C30" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>10.51895172413793</v>
+        <v>2.5201785714285716</v>
       </c>
       <c r="D30" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>21.186206896551724</v>
+        <v>3.9285714285714293</v>
       </c>
       <c r="E30" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>52.965517241379317</v>
+        <v>7.1428571428571432</v>
       </c>
       <c r="F30">
-        <v>35.9</v>
+        <v>47.9</v>
       </c>
       <c r="G30" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.39999999999999997</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="H30">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="I30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K30">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L30">
-        <v>4.25</v>
+        <v>6.5</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N30">
-        <v>720</v>
-      </c>
-      <c r="O30" s="2">
-        <f t="shared" si="2"/>
-        <v>8.3333333333333329E-2</v>
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>6.5</v>
       </c>
       <c r="P30">
         <v>0.2</v>
       </c>
       <c r="Q30">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="R30">
-        <v>0.61</v>
+        <v>0.7</v>
       </c>
       <c r="S30">
-        <v>0.32</v>
+        <v>0.9</v>
       </c>
       <c r="T30">
-        <v>5.9</v>
+        <v>10.9</v>
       </c>
       <c r="U30">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="V30">
         <v>115</v>
       </c>
       <c r="W30">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="X30" s="33" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Y30">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AA30" s="2">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.22222222222222221</v>
+        <v>0.25</v>
       </c>
       <c r="AC30" s="92" t="s">
         <v>326</v>
@@ -15026,16 +15014,16 @@
         <v>87</v>
       </c>
       <c r="AE30" s="44">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="AF30" t="s">
-        <v>434</v>
-      </c>
-      <c r="AI30" s="12" t="s">
-        <v>103</v>
+        <v>432</v>
+      </c>
+      <c r="AI30" s="12">
+        <v>1.9</v>
       </c>
       <c r="AJ30" s="12">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="31" spans="1:36">
@@ -15047,7 +15035,7 @@
       </c>
       <c r="C31" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>2.3568300000000004</v>
+        <v>2.6083800000000004</v>
       </c>
       <c r="D31" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
@@ -15055,75 +15043,75 @@
       </c>
       <c r="E31" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>6.88</v>
+        <v>7.2</v>
       </c>
       <c r="F31">
-        <v>45.9</v>
+        <v>49.9</v>
       </c>
       <c r="G31" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.5625</v>
+        <v>0.53749999999999998</v>
       </c>
       <c r="H31">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="I31">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J31">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="N31">
         <v>0</v>
       </c>
       <c r="O31">
-        <v>6</v>
-      </c>
-      <c r="P31">
+        <v>7</v>
+      </c>
+      <c r="P31" s="7">
         <v>0.2</v>
       </c>
-      <c r="Q31">
-        <v>0.4</v>
-      </c>
-      <c r="R31">
+      <c r="Q31" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="R31" s="7">
         <v>0.7</v>
       </c>
-      <c r="S31">
-        <v>0.95</v>
-      </c>
-      <c r="T31">
-        <v>9.9</v>
+      <c r="S31" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="T31" s="7">
+        <v>12.9</v>
       </c>
       <c r="U31">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="V31">
-        <v>105</v>
-      </c>
-      <c r="W31">
-        <v>40</v>
+        <v>135</v>
+      </c>
+      <c r="W31" s="7">
+        <v>50</v>
       </c>
       <c r="X31" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="Y31">
+      <c r="Y31" s="7">
         <v>10</v>
       </c>
-      <c r="Z31">
+      <c r="Z31" s="7">
         <v>10</v>
       </c>
       <c r="AA31" s="2">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AC31" s="92" t="s">
         <v>326</v>
@@ -15132,16 +15120,16 @@
         <v>87</v>
       </c>
       <c r="AE31" s="44">
-        <v>-250</v>
+        <v>-350</v>
       </c>
       <c r="AF31" t="s">
-        <v>434</v>
-      </c>
-      <c r="AI31" s="12" t="s">
-        <v>103</v>
+        <v>432</v>
+      </c>
+      <c r="AI31" s="12">
+        <v>3.9</v>
       </c>
       <c r="AJ31" s="12">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="32" spans="1:36">
@@ -15153,37 +15141,37 @@
       </c>
       <c r="C32" s="2">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>2.5201785714285716</v>
+        <v>5.7305454545454531</v>
       </c>
       <c r="D32" s="3">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>3.9285714285714293</v>
+        <v>6.9545454545454533</v>
       </c>
       <c r="E32" s="2">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>7.1428571428571432</v>
+        <v>10.909090909090908</v>
       </c>
       <c r="F32">
-        <v>47.9</v>
+        <v>54.9</v>
       </c>
       <c r="G32" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.55000000000000004</v>
+        <v>0.63749999999999996</v>
       </c>
       <c r="H32">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J32">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>0.5</v>
@@ -15192,277 +15180,122 @@
         <v>0</v>
       </c>
       <c r="O32">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="P32">
         <v>0.2</v>
       </c>
       <c r="Q32">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="R32">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="S32">
         <v>0.9</v>
       </c>
       <c r="T32">
-        <v>10.9</v>
+        <v>5.9</v>
       </c>
       <c r="U32">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="V32">
-        <v>115</v>
-      </c>
-      <c r="W32">
-        <v>50</v>
+        <v>80</v>
+      </c>
+      <c r="W32" s="33">
+        <v>90</v>
       </c>
       <c r="X32" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="Y32">
-        <v>10</v>
-      </c>
-      <c r="Z32">
-        <v>10</v>
+        <v>322</v>
+      </c>
+      <c r="Y32" s="33">
+        <v>30</v>
+      </c>
+      <c r="Z32" s="33">
+        <v>30</v>
       </c>
       <c r="AA32" s="2">
         <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.2</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AC32" s="92" t="s">
         <v>326</v>
       </c>
       <c r="AD32" s="44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AE32" s="44">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="s">
-        <v>434</v>
-      </c>
-      <c r="AI32" s="12">
-        <v>1.9</v>
-      </c>
-      <c r="AJ32" s="12">
-        <v>3.5</v>
+        <v>432</v>
+      </c>
+      <c r="AI32" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ32" s="12" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:36">
-      <c r="A33" t="s">
-        <v>480</v>
-      </c>
       <c r="B33" s="33" t="s">
         <v>288</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="2" t="e">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>2.6083800000000004</v>
-      </c>
-      <c r="D33" s="3">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D33" s="3" t="e">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>3.87</v>
-      </c>
-      <c r="E33" s="2">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E33" s="2" t="e">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>7.2</v>
-      </c>
-      <c r="F33">
-        <v>49.9</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G33" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.53749999999999998</v>
-      </c>
-      <c r="H33">
-        <v>54</v>
-      </c>
-      <c r="I33">
-        <v>3</v>
-      </c>
-      <c r="J33">
-        <v>70</v>
-      </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-      <c r="L33">
-        <v>7</v>
-      </c>
-      <c r="M33">
-        <v>0.5</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>7</v>
-      </c>
-      <c r="P33" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="Q33" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="R33" s="7">
-        <v>0.7</v>
-      </c>
-      <c r="S33" s="7">
-        <v>0.9</v>
-      </c>
-      <c r="T33" s="7">
-        <v>12.9</v>
-      </c>
-      <c r="V33">
-        <v>135</v>
-      </c>
-      <c r="W33" s="7">
-        <v>70</v>
-      </c>
-      <c r="X33" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="Y33" s="7">
-        <v>10</v>
-      </c>
-      <c r="Z33" s="7">
-        <v>10</v>
-      </c>
-      <c r="AA33" s="2">
-        <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="AC33" s="92" t="s">
-        <v>326</v>
-      </c>
-      <c r="AD33" s="44" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE33" s="44">
-        <v>-350</v>
-      </c>
-      <c r="AF33" t="s">
-        <v>434</v>
-      </c>
-      <c r="AI33" s="12">
-        <v>3.9</v>
-      </c>
-      <c r="AJ33" s="12">
-        <v>4.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD33" s="44"/>
+      <c r="AE33" s="44"/>
+      <c r="AI33" s="12"/>
+      <c r="AJ33" s="12"/>
     </row>
     <row r="34" spans="1:36">
-      <c r="A34" t="s">
-        <v>481</v>
-      </c>
-      <c r="B34" s="33" t="s">
-        <v>288</v>
-      </c>
-      <c r="C34" s="2">
+      <c r="B34" s="33"/>
+      <c r="C34" s="2" t="e">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>5.7305454545454531</v>
-      </c>
-      <c r="D34" s="3">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D34" s="3" t="e">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>6.9545454545454533</v>
-      </c>
-      <c r="E34" s="2">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E34" s="2" t="e">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>10.909090909090908</v>
-      </c>
-      <c r="F34">
-        <v>54.9</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G34" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0.63749999999999996</v>
-      </c>
-      <c r="H34">
-        <v>60</v>
-      </c>
-      <c r="I34">
-        <v>5</v>
-      </c>
-      <c r="J34">
-        <v>110</v>
-      </c>
-      <c r="K34">
-        <v>1</v>
-      </c>
-      <c r="L34">
-        <v>5</v>
-      </c>
-      <c r="M34">
-        <v>0.5</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>5</v>
-      </c>
-      <c r="P34">
-        <v>0.2</v>
-      </c>
-      <c r="Q34">
-        <v>0.5</v>
-      </c>
-      <c r="R34">
-        <v>0.95</v>
-      </c>
-      <c r="S34">
-        <v>0.9</v>
-      </c>
-      <c r="T34">
-        <v>5.9</v>
-      </c>
-      <c r="U34">
-        <v>300</v>
-      </c>
-      <c r="V34">
-        <v>80</v>
-      </c>
-      <c r="W34" s="33">
-        <v>90</v>
-      </c>
-      <c r="X34" s="33" t="s">
-        <v>322</v>
-      </c>
-      <c r="Y34" s="33">
-        <v>30</v>
-      </c>
-      <c r="Z34" s="33">
-        <v>30</v>
-      </c>
-      <c r="AA34" s="2">
-        <f>Table16810111245[[#This Row],[Ammo]]/Table16810111245[[#This Row],[Rearm Cost]]</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="AC34" s="92" t="s">
-        <v>326</v>
-      </c>
-      <c r="AD34" s="44" t="s">
-        <v>86</v>
-      </c>
-      <c r="AE34" s="44">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="s">
-        <v>434</v>
-      </c>
-      <c r="AI34" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="AJ34" s="12" t="s">
-        <v>103</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD34" s="44"/>
+      <c r="AE34" s="44"/>
+      <c r="AI34" s="12"/>
+      <c r="AJ34" s="12"/>
     </row>
     <row r="35" spans="1:36">
-      <c r="B35" s="33" t="s">
-        <v>288</v>
-      </c>
+      <c r="B35" s="33"/>
       <c r="C35" s="2" t="e">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
         <v>#DIV/0!</v>
@@ -15597,29 +15430,55 @@
       <c r="AJ39" s="12"/>
     </row>
     <row r="40" spans="1:36">
-      <c r="B40" s="33"/>
-      <c r="C40" s="2" t="e">
+      <c r="A40" s="7"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="8" t="e">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D40" s="3" t="e">
+      <c r="D40" s="9" t="e">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E40" s="2" t="e">
+      <c r="E40" s="8" t="e">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="G40" s="2">
+      <c r="F40" s="7"/>
+      <c r="G40" s="8">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
         <v>0</v>
       </c>
-      <c r="O40" s="2" t="e">
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
+      <c r="O40" s="8" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD40" s="44"/>
-      <c r="AE40" s="44"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="7"/>
+      <c r="V40" s="7"/>
+      <c r="W40" s="7"/>
+      <c r="X40" s="37"/>
+      <c r="Y40" s="7"/>
+      <c r="Z40" s="7"/>
+      <c r="AA40" s="7"/>
+      <c r="AB40" s="7"/>
+      <c r="AC40" s="7"/>
+      <c r="AD40" s="52"/>
+      <c r="AE40" s="52"/>
+      <c r="AF40" s="7"/>
+      <c r="AG40" s="7"/>
+      <c r="AH40" s="7"/>
       <c r="AI40" s="12"/>
       <c r="AJ40" s="12"/>
     </row>
@@ -15642,7 +15501,7 @@
         <v>0</v>
       </c>
       <c r="O41" s="2" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="O41:O48" si="3">60/N41</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AD41" s="44"/>
@@ -15651,55 +15510,29 @@
       <c r="AJ41" s="12"/>
     </row>
     <row r="42" spans="1:36">
-      <c r="A42" s="7"/>
-      <c r="B42" s="37"/>
-      <c r="C42" s="8" t="e">
+      <c r="B42" s="33"/>
+      <c r="C42" s="2" t="e">
         <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D42" s="9" t="e">
+      <c r="D42" s="3" t="e">
         <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E42" s="8" t="e">
+      <c r="E42" s="2" t="e">
         <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F42" s="7"/>
-      <c r="G42" s="8">
+      <c r="G42" s="2">
         <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
         <v>0</v>
       </c>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="N42" s="7"/>
-      <c r="O42" s="8" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="7"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="7"/>
-      <c r="T42" s="7"/>
-      <c r="U42" s="7"/>
-      <c r="V42" s="7"/>
-      <c r="W42" s="7"/>
-      <c r="X42" s="37"/>
-      <c r="Y42" s="7"/>
-      <c r="Z42" s="7"/>
-      <c r="AA42" s="7"/>
-      <c r="AB42" s="7"/>
-      <c r="AC42" s="7"/>
-      <c r="AD42" s="52"/>
-      <c r="AE42" s="52"/>
-      <c r="AF42" s="7"/>
-      <c r="AG42" s="7"/>
-      <c r="AH42" s="7"/>
+      <c r="O42" s="2" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD42" s="44"/>
+      <c r="AE42" s="44"/>
       <c r="AI42" s="12"/>
       <c r="AJ42" s="12"/>
     </row>
@@ -15722,7 +15555,7 @@
         <v>0</v>
       </c>
       <c r="O43" s="2" t="e">
-        <f t="shared" ref="O43:O50" si="3">60/N43</f>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="AD43" s="44"/>
@@ -15862,66 +15695,12 @@
       </c>
       <c r="AD48" s="44"/>
       <c r="AE48" s="44"/>
-      <c r="AI48" s="12"/>
-      <c r="AJ48" s="12"/>
-    </row>
-    <row r="49" spans="2:36">
-      <c r="B49" s="33"/>
-      <c r="C49" s="2" t="e">
-        <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D49" s="3" t="e">
-        <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E49" s="2" t="e">
-        <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G49" s="2">
-        <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0</v>
-      </c>
-      <c r="O49" s="2" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD49" s="44"/>
-      <c r="AE49" s="44"/>
-      <c r="AI49" s="12"/>
-      <c r="AJ49" s="12"/>
-    </row>
-    <row r="50" spans="2:36">
-      <c r="B50" s="33"/>
-      <c r="C50" s="2" t="e">
-        <f>SUM(((Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Range]]))+(Table16810111245[[#This Row],[Avg DPS]]*(Table16810111245[[#This Row],[Arm Pen (%)]]/4)))/100)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D50" s="3" t="e">
-        <f>SUM(Table16810111245[[#This Row],[DPS]]*Table16810111245[[#This Row],[Avg Accuracy]])</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E50" s="2" t="e">
-        <f>SUM((Table16810111245[[#This Row],[Damage]]*Table16810111245[[#This Row],[Burst]])/(Table16810111245[[#This Row],[Ranged Cooldown]]+Table16810111245[[#This Row],[Warm-up]]+(Table16810111245[[#This Row],[Burst Time]]*(Table16810111245[[#This Row],[Burst]]-1))))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G50" s="2">
-        <f>SUM((Table16810111245[[#This Row],[Accuracy (Close)]]+Table16810111245[[#This Row],[Accuracy (Short)]]+Table16810111245[[#This Row],[Accuracy (Medium)]]+Table16810111245[[#This Row],[Accuracy (Long)]])/4)</f>
-        <v>0</v>
-      </c>
-      <c r="O50" s="2" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD50" s="44"/>
-      <c r="AE50" s="44"/>
-      <c r="AI50" s="13"/>
-      <c r="AJ50" s="13"/>
+      <c r="AI48" s="13"/>
+      <c r="AJ48" s="13"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F4:F50">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="F4:F48">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -15977,7 +15756,7 @@
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H1" s="89"/>
       <c r="I1" s="89"/>
@@ -16663,7 +16442,7 @@
     </row>
     <row r="14" spans="1:21" s="4" customFormat="1">
       <c r="A14" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B14" s="10">
         <v>4</v>
@@ -16713,7 +16492,7 @@
       <c r="Q14" s="31"/>
       <c r="R14" s="31"/>
       <c r="S14" s="28" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="T14" s="66" t="s">
         <v>339</v>
@@ -16787,7 +16566,7 @@
     </row>
     <row r="16" spans="1:21">
       <c r="A16" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B16">
         <v>4</v>
@@ -17013,7 +16792,7 @@
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="4" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B20" s="4">
         <v>5</v>
@@ -17063,7 +16842,7 @@
       <c r="Q20" s="28"/>
       <c r="R20" s="28"/>
       <c r="S20" s="28" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="T20" s="66" t="s">
         <v>339</v>
@@ -17751,7 +17530,7 @@
         <v>24</v>
       </c>
       <c r="F1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G1" s="89"/>
       <c r="H1" s="89"/>
@@ -18097,7 +17876,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C11">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="greaterThan">
       <formula>3.51</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18138,13 +17917,13 @@
         <v>255</v>
       </c>
       <c r="G1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H1" t="s">
+        <v>515</v>
+      </c>
+      <c r="I1" t="s">
         <v>517</v>
-      </c>
-      <c r="I1" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -18851,10 +18630,10 @@
         <v>4.3478260869565224</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E27" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -18866,10 +18645,10 @@
         <v>4.545454545454545</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E28" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -18881,10 +18660,10 @@
         <v>4.7619047619047619</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E29" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -18896,10 +18675,10 @@
         <v>5.25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E30" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -19050,47 +18829,47 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D33">
-    <cfRule type="cellIs" dxfId="12" priority="7" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="11" priority="7" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>18.15</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="10" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>17.36</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="9" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="9" operator="greaterThanOrEqual">
       <formula>16.57</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="10" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="8" priority="10" stopIfTrue="1" operator="between">
       <formula>13.72</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="11" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="7" priority="11" stopIfTrue="1" operator="between">
       <formula>14.35</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="12" operator="between">
+    <cfRule type="cellIs" dxfId="6" priority="12" operator="between">
       <formula>15.03</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="cellIs" dxfId="6" priority="1" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="1" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.43</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="2" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="4" priority="2" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.41</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThanOrEqual">
       <formula>0.39</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="2" priority="4" stopIfTrue="1" operator="between">
       <formula>0.32</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="5" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="5" stopIfTrue="1" operator="between">
       <formula>0.34</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="between">
       <formula>0.35</formula>
       <formula>0.01</formula>
     </cfRule>
@@ -50244,7 +50023,7 @@
         <v>69</v>
       </c>
       <c r="I1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J1" s="89"/>
       <c r="K1" s="89"/>
@@ -50354,7 +50133,7 @@
     </row>
     <row r="4" spans="1:25">
       <c r="A4" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B4" s="12">
         <v>4</v>
@@ -50428,10 +50207,10 @@
         <v>133.68375</v>
       </c>
       <c r="X4" t="s">
+        <v>485</v>
+      </c>
+      <c r="Y4" t="s">
         <v>487</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -50510,10 +50289,10 @@
         <v>136.94803977272727</v>
       </c>
       <c r="X5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="Y5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -50592,10 +50371,10 @@
         <v>143.62701923076924</v>
       </c>
       <c r="X6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="Y6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -50674,10 +50453,10 @@
         <v>128.82354294478526</v>
       </c>
       <c r="X7" t="s">
+        <v>485</v>
+      </c>
+      <c r="Y7" t="s">
         <v>487</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="8" spans="1:25" s="70" customFormat="1">
@@ -51134,71 +50913,71 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C500">
-    <cfRule type="cellIs" dxfId="361" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="360" priority="17" operator="greaterThan">
       <formula>1.209</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:O1048576">
-    <cfRule type="cellIs" dxfId="360" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="359" priority="16" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E500">
-    <cfRule type="cellIs" dxfId="359" priority="15" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="358" priority="15" operator="greaterThanOrEqual">
       <formula>6.64</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="358" priority="13" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="357" priority="13" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>7.27</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="357" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="356" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>6.95</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="356" priority="7" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="355" priority="7" stopIfTrue="1" operator="between">
       <formula>5.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="355" priority="8" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="354" priority="8" stopIfTrue="1" operator="between">
       <formula>5.75</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="354" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="353" priority="9" operator="between">
       <formula>6.02</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G500">
-    <cfRule type="cellIs" dxfId="353" priority="10" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="352" priority="10" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.72</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="352" priority="11" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="351" priority="11" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.69</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="351" priority="12" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="350" priority="12" operator="greaterThanOrEqual">
       <formula>0.66</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="350" priority="1" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="349" priority="1" stopIfTrue="1" operator="between">
       <formula>0.55</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="349" priority="2" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="348" priority="2" stopIfTrue="1" operator="between">
       <formula>0.57</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="348" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="347" priority="3" operator="between">
       <formula>0.6</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F500">
-    <cfRule type="cellIs" dxfId="347" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="346" priority="6" operator="between">
       <formula>23.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="346" priority="4" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="345" priority="4" stopIfTrue="1" operator="between">
       <formula>19.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="345" priority="5" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="344" priority="5" stopIfTrue="1" operator="between">
       <formula>21.9</formula>
       <formula>0.01</formula>
     </cfRule>
@@ -51250,7 +51029,7 @@
         <v>77</v>
       </c>
       <c r="H1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I1" s="89"/>
       <c r="J1" s="89"/>
@@ -51857,7 +51636,7 @@
     </row>
     <row r="10" spans="1:25" s="4" customFormat="1">
       <c r="A10" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B10" s="12">
         <v>7</v>
@@ -52613,78 +52392,78 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C500">
-    <cfRule type="cellIs" dxfId="337" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="336" priority="19" operator="greaterThan">
       <formula>1.259</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:O1048576">
-    <cfRule type="cellIs" dxfId="336" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="335" priority="18" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E500">
-    <cfRule type="cellIs" dxfId="335" priority="12" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="334" priority="12" stopIfTrue="1" operator="between">
       <formula>9.57</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="334" priority="13" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="333" priority="13" stopIfTrue="1" operator="between">
       <formula>10.01</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="333" priority="14" operator="between">
+    <cfRule type="cellIs" dxfId="332" priority="14" operator="between">
       <formula>10.49</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="332" priority="15" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="331" priority="15" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>12.66</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="331" priority="16" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="330" priority="16" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>12.11</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="330" priority="17" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="329" priority="17" operator="greaterThanOrEqual">
       <formula>11.56</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F500">
-    <cfRule type="cellIs" dxfId="329" priority="7" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="328" priority="7" stopIfTrue="1" operator="between">
       <formula>13.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="328" priority="8" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="327" priority="8" stopIfTrue="1" operator="between">
       <formula>15.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="327" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="326" priority="9" operator="between">
       <formula>17.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="326" priority="10" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="325" priority="10" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>22.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="325" priority="11" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="324" priority="11" operator="greaterThanOrEqual">
       <formula>21.9</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G500">
-    <cfRule type="cellIs" dxfId="324" priority="1" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="323" priority="1" stopIfTrue="1" operator="between">
       <formula>0.44</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="323" priority="2" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="322" priority="2" stopIfTrue="1" operator="between">
       <formula>0.46</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="322" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="321" priority="3" operator="between">
       <formula>0.49</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="321" priority="4" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="320" priority="4" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.59</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="320" priority="5" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="319" priority="5" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.56</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="319" priority="6" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="318" priority="6" operator="greaterThanOrEqual">
       <formula>0.54</formula>
     </cfRule>
   </conditionalFormatting>
@@ -52734,7 +52513,7 @@
         <v>77</v>
       </c>
       <c r="H1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="I1" s="89"/>
       <c r="J1" s="89"/>
@@ -53666,10 +53445,10 @@
         <v>320.25490714285712</v>
       </c>
       <c r="X13" s="47" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="Y13" s="47" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -53840,7 +53619,7 @@
     </row>
     <row r="16" spans="1:25" s="70" customFormat="1">
       <c r="A16" s="88" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B16" s="12">
         <v>5</v>
@@ -53915,15 +53694,15 @@
         <v>341.74395169811316</v>
       </c>
       <c r="X16" s="47" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="Y16" s="47" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="17" spans="1:25">
       <c r="A17" s="4" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B17" s="12">
         <v>5</v>
@@ -53998,15 +53777,15 @@
         <v>320.16817642585551</v>
       </c>
       <c r="X17" s="47" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="Y17" s="47" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="4" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B18" s="12">
         <v>5</v>
@@ -54081,15 +53860,15 @@
         <v>334.50662686567159</v>
       </c>
       <c r="X18" s="47" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="Y18" s="47" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="19" spans="1:25">
       <c r="A19" s="4" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B19" s="4">
         <v>5</v>
@@ -54163,10 +53942,10 @@
         <v>340.51474285714283</v>
       </c>
       <c r="X19" s="47" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="Y19" s="47" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -54601,72 +54380,72 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C500">
-    <cfRule type="cellIs" dxfId="308" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="307" priority="17" operator="greaterThan">
       <formula>1.739</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:O1048576">
-    <cfRule type="cellIs" dxfId="307" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="306" priority="16" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E500">
-    <cfRule type="cellIs" dxfId="306" priority="13" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="305" priority="13" stopIfTrue="1" operator="between">
       <formula>10.73</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="305" priority="14" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="304" priority="14" stopIfTrue="1" operator="between">
       <formula>11.22</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="304" priority="15" operator="between">
+    <cfRule type="cellIs" dxfId="303" priority="15" operator="between">
       <formula>11.75</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="303" priority="10" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="302" priority="10" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>14.19</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="302" priority="11" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="301" priority="11" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>13.57</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="301" priority="12" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="300" priority="12" operator="greaterThanOrEqual">
       <formula>12.96</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F500">
-    <cfRule type="cellIs" dxfId="300" priority="7" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="299" priority="7" stopIfTrue="1" operator="between">
       <formula>16.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="299" priority="8" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="298" priority="8" stopIfTrue="1" operator="between">
       <formula>18.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="298" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="297" priority="9" operator="between">
       <formula>20.9</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G500">
-    <cfRule type="cellIs" dxfId="297" priority="1" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="296" priority="1" stopIfTrue="1" operator="between">
       <formula>0.44</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="296" priority="2" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="295" priority="2" stopIfTrue="1" operator="between">
       <formula>0.46</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="295" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="294" priority="3" operator="between">
       <formula>0.49</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="294" priority="4" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="293" priority="4" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.59</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="293" priority="5" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="292" priority="5" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.56</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="292" priority="6" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="291" priority="6" operator="greaterThanOrEqual">
       <formula>0.54</formula>
     </cfRule>
   </conditionalFormatting>
@@ -54726,7 +54505,7 @@
         <v>76</v>
       </c>
       <c r="J1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K1" s="89"/>
       <c r="L1" s="89"/>
@@ -57567,7 +57346,7 @@
         <v>437.33909172413792</v>
       </c>
       <c r="X34" s="34" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y34" s="34" t="s">
         <v>383</v>
@@ -57668,7 +57447,7 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" s="14" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -58093,10 +57872,10 @@
         <v>461.7549800173565</v>
       </c>
       <c r="X40" s="34" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="Y40" s="34" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Z40" s="33"/>
       <c r="AA40" s="33"/>
@@ -58106,7 +57885,7 @@
     </row>
     <row r="41" spans="1:30" s="70" customFormat="1">
       <c r="A41" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B41">
         <v>4</v>
@@ -58181,7 +57960,7 @@
         <v>499.36223178947364</v>
       </c>
       <c r="X41" s="34" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="Y41" s="34" t="s">
         <v>383</v>
@@ -58194,7 +57973,7 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B42">
         <v>4</v>
@@ -58271,7 +58050,7 @@
         <v>398</v>
       </c>
       <c r="Y42" s="34" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="Z42" s="33"/>
       <c r="AA42" s="33"/>
@@ -58281,7 +58060,7 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" s="14" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B43">
         <v>5</v>
@@ -58317,7 +58096,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X43" s="34" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Y43" s="34" t="s">
         <v>403</v>
@@ -58330,7 +58109,7 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B44">
         <v>5</v>
@@ -58366,10 +58145,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X44" s="34" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="Y44" s="34" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="Z44" s="33"/>
       <c r="AA44" s="33"/>
@@ -61312,80 +61091,80 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C997">
-    <cfRule type="cellIs" dxfId="283" priority="20" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="282" priority="20" operator="greaterThan">
       <formula>2.419</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:O500">
-    <cfRule type="cellIs" dxfId="282" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="281" priority="19" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F500">
-    <cfRule type="cellIs" dxfId="281" priority="7" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="280" priority="7" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>36.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="280" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="279" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>34.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="279" priority="9" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="278" priority="9" operator="greaterThanOrEqual">
       <formula>32.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="278" priority="10" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="277" priority="10" stopIfTrue="1" operator="between">
       <formula>24.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="277" priority="11" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="276" priority="11" stopIfTrue="1" operator="between">
       <formula>26.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="276" priority="12" operator="between">
+    <cfRule type="cellIs" dxfId="275" priority="12" operator="between">
       <formula>28.5</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G500">
-    <cfRule type="cellIs" dxfId="275" priority="1" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="274" priority="1" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.72</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="274" priority="2" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="273" priority="2" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.69</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="273" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="272" priority="3" operator="greaterThanOrEqual">
       <formula>0.66</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="272" priority="4" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="271" priority="4" stopIfTrue="1" operator="between">
       <formula>0.54</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="271" priority="5" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="270" priority="5" stopIfTrue="1" operator="between">
       <formula>0.57</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="270" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="269" priority="6" operator="between">
       <formula>0.6</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E500">
-    <cfRule type="cellIs" dxfId="269" priority="13" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="268" priority="13" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>12.51</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="268" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="267" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>11.97</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="267" priority="15" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="266" priority="15" operator="greaterThanOrEqual">
       <formula>11.42</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="266" priority="16" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="265" priority="16" stopIfTrue="1" operator="between">
       <formula>9.46</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="265" priority="17" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="264" priority="17" stopIfTrue="1" operator="between">
       <formula>9.89</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="264" priority="18" operator="between">
+    <cfRule type="cellIs" dxfId="263" priority="18" operator="between">
       <formula>10.36</formula>
       <formula>0.01</formula>
     </cfRule>
@@ -61444,7 +61223,7 @@
         <v>76</v>
       </c>
       <c r="J1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K1" s="89"/>
       <c r="L1" s="89"/>
@@ -62179,7 +61958,7 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B11" s="4">
         <v>4</v>
@@ -62340,10 +62119,10 @@
         <v>250.31141694915254</v>
       </c>
       <c r="X12" s="87" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="Y12" s="34" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="Z12" s="50"/>
       <c r="AA12" s="50"/>
@@ -66443,80 +66222,80 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C997">
-    <cfRule type="cellIs" dxfId="247" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="246" priority="21" operator="greaterThan">
       <formula>1.939</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O4:O500">
-    <cfRule type="cellIs" dxfId="246" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="245" priority="20" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E500">
-    <cfRule type="cellIs" dxfId="245" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="244" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>6.47</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="244" priority="15" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="243" priority="15" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>6.19</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="243" priority="16" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="242" priority="16" operator="greaterThanOrEqual">
       <formula>5.91</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="242" priority="17" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="241" priority="17" stopIfTrue="1" operator="between">
       <formula>4.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="241" priority="18" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="240" priority="18" stopIfTrue="1" operator="between">
       <formula>5.12</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="240" priority="19" operator="between">
+    <cfRule type="cellIs" dxfId="239" priority="19" operator="between">
       <formula>5.36</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F500">
-    <cfRule type="cellIs" dxfId="239" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="238" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>42.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="238" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="237" priority="9" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>40.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="237" priority="10" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="236" priority="10" operator="greaterThanOrEqual">
       <formula>38.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="236" priority="11" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="235" priority="11" stopIfTrue="1" operator="between">
       <formula>30.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="235" priority="12" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="234" priority="12" stopIfTrue="1" operator="between">
       <formula>32.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="234" priority="13" operator="between">
+    <cfRule type="cellIs" dxfId="233" priority="13" operator="between">
       <formula>34.9</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G500">
-    <cfRule type="cellIs" dxfId="233" priority="1" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="232" priority="1" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.91</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="232" priority="3" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="231" priority="3" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.87</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="231" priority="4" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="230" priority="4" operator="greaterThanOrEqual">
       <formula>0.83</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="230" priority="5" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="229" priority="5" stopIfTrue="1" operator="between">
       <formula>0.69</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="229" priority="6" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="228" priority="6" stopIfTrue="1" operator="between">
       <formula>0.72</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="228" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="227" priority="7" operator="between">
       <formula>0.75</formula>
       <formula>0.01</formula>
     </cfRule>
@@ -66570,7 +66349,7 @@
         <v>239</v>
       </c>
       <c r="M1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="N1" s="89"/>
       <c r="O1" s="89"/>
@@ -67655,7 +67434,7 @@
         <v>543.19706999999994</v>
       </c>
       <c r="X15" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="Y15" t="s">
         <v>397</v>
@@ -67745,7 +67524,7 @@
     </row>
     <row r="17" spans="1:25" s="4" customFormat="1">
       <c r="A17" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B17" s="4">
         <v>4</v>
@@ -67819,7 +67598,7 @@
         <v>591.63690253846141</v>
       </c>
       <c r="X17" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="Y17" t="s">
         <v>365</v>
@@ -67827,7 +67606,7 @@
     </row>
     <row r="18" spans="1:25" s="70" customFormat="1">
       <c r="A18" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B18">
         <v>4</v>
@@ -67901,10 +67680,10 @@
         <v>575.17852431818187</v>
       </c>
       <c r="X18" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="Y18" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -68468,81 +68247,81 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C500">
-    <cfRule type="cellIs" dxfId="211" priority="20" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="210" priority="20" operator="greaterThan">
       <formula>2.1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O2:O1048576">
-    <cfRule type="cellIs" dxfId="210" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="209" priority="19" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E500">
-    <cfRule type="cellIs" dxfId="209" priority="13" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="208" priority="13" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>5.75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="208" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="207" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>5.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="207" priority="15" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="206" priority="15" operator="greaterThanOrEqual">
       <formula>5.25</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="206" priority="16" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="205" priority="16" stopIfTrue="1" operator="between">
       <formula>4.35</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="205" priority="17" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="204" priority="17" stopIfTrue="1" operator="between">
       <formula>4.55</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="204" priority="18" operator="between">
+    <cfRule type="cellIs" dxfId="203" priority="18" operator="between">
       <formula>4.76</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F500">
-    <cfRule type="cellIs" dxfId="203" priority="7" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="202" priority="7" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>50.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="202" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="201" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>48.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="201" priority="9" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="200" priority="9" operator="greaterThanOrEqual">
       <formula>46.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="200" priority="10" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="199" priority="10" stopIfTrue="1" operator="between">
       <formula>38.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="199" priority="11" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="198" priority="11" stopIfTrue="1" operator="between">
       <formula>40.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="198" priority="12" operator="between">
+    <cfRule type="cellIs" dxfId="197" priority="12" operator="between">
       <formula>42.9</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G500">
-    <cfRule type="cellIs" dxfId="197" priority="4" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="196" priority="4" stopIfTrue="1" operator="between">
       <formula>0.65</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="5" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="195" priority="5" stopIfTrue="1" operator="between">
       <formula>0.68</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="195" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="194" priority="6" operator="between">
       <formula>0.71</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="194" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="193" priority="3" operator="greaterThanOrEqual">
       <formula>0.79</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="2" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="192" priority="2" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.83</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="1" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="191" priority="1" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.86</formula>
     </cfRule>
   </conditionalFormatting>
@@ -68590,7 +68369,7 @@
         <v>66</v>
       </c>
       <c r="K1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="L1" s="89"/>
       <c r="M1" s="89"/>
@@ -69487,7 +69266,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C500">
-    <cfRule type="cellIs" dxfId="185" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="184" priority="1" operator="greaterThan">
       <formula>2.839</formula>
     </cfRule>
   </conditionalFormatting>
@@ -69542,7 +69321,7 @@
         <v>74</v>
       </c>
       <c r="K1" s="89" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="L1" s="89"/>
       <c r="M1" s="89"/>
@@ -70314,7 +70093,7 @@
         <v>510.41361253012042</v>
       </c>
       <c r="X11" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="Y11" t="s">
         <v>363</v>
@@ -70322,7 +70101,7 @@
     </row>
     <row r="12" spans="1:25" s="70" customFormat="1">
       <c r="A12" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B12">
         <v>4</v>
@@ -70397,15 +70176,15 @@
         <v>529.21317600000009</v>
       </c>
       <c r="X12" t="s">
+        <v>506</v>
+      </c>
+      <c r="Y12" t="s">
         <v>508</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:25">
       <c r="A13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B13">
         <v>4</v>
@@ -70480,15 +70259,15 @@
         <v>497.13965018181813</v>
       </c>
       <c r="X13" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="Y13" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="14" spans="1:25">
       <c r="A14" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -70518,10 +70297,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="X14" t="s">
+        <v>507</v>
+      </c>
+      <c r="Y14" t="s">
         <v>509</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -70820,75 +70599,75 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C4:C500">
-    <cfRule type="cellIs" dxfId="179" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="178" priority="19" operator="greaterThan">
       <formula>3.189</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4:E500">
-    <cfRule type="cellIs" dxfId="178" priority="13" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="177" priority="13" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>20.79</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="176" priority="14" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>19.89</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="176" priority="15" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="175" priority="15" operator="greaterThanOrEqual">
       <formula>18.98</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="16" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="174" priority="16" stopIfTrue="1" operator="between">
       <formula>15.72</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="174" priority="17" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="173" priority="17" stopIfTrue="1" operator="between">
       <formula>16.44</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="173" priority="18" operator="between">
+    <cfRule type="cellIs" dxfId="172" priority="18" operator="between">
       <formula>17.22</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F500">
-    <cfRule type="cellIs" dxfId="172" priority="7" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="171" priority="7" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>31.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="171" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="170" priority="8" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>29.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="170" priority="9" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="169" priority="9" operator="greaterThanOrEqual">
       <formula>27.9</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="169" priority="10" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="168" priority="10" stopIfTrue="1" operator="between">
       <formula>19.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="11" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="167" priority="11" stopIfTrue="1" operator="between">
       <formula>21.9</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="167" priority="12" operator="between">
+    <cfRule type="cellIs" dxfId="166" priority="12" operator="between">
       <formula>23.9</formula>
       <formula>0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4:G500">
-    <cfRule type="cellIs" dxfId="166" priority="1" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="165" priority="1" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.43</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="2" stopIfTrue="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="164" priority="2" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0.41</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="164" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="163" priority="3" operator="greaterThanOrEqual">
       <formula>0.39</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="163" priority="4" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="162" priority="4" stopIfTrue="1" operator="between">
       <formula>0.32</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="5" stopIfTrue="1" operator="between">
+    <cfRule type="cellIs" dxfId="161" priority="5" stopIfTrue="1" operator="between">
       <formula>0.34</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="161" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="160" priority="6" operator="between">
       <formula>0.35</formula>
       <formula>0.01</formula>
     </cfRule>
